--- a/FlowTracker.xlsx
+++ b/FlowTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD58BE99-8F09-4910-8DC2-7E720DCC77A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82BE0D7-A75C-49CA-B5B1-B5F889AFF77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21697" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2280" uniqueCount="799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2283" uniqueCount="799">
   <si>
     <t>Filename</t>
   </si>
@@ -5672,6 +5672,9 @@
       <c r="A8" t="s">
         <v>782</v>
       </c>
+      <c r="H8" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -5688,6 +5691,9 @@
       <c r="A10" t="s">
         <v>784</v>
       </c>
+      <c r="H10" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -5695,6 +5701,9 @@
       </c>
       <c r="D11" t="s">
         <v>784</v>
+      </c>
+      <c r="H11" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/FlowTracker.xlsx
+++ b/FlowTracker.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82BE0D7-A75C-49CA-B5B1-B5F889AFF77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E42B821-236F-48BB-99C7-5A484EDEB984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21697" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21697" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="arteries" sheetId="1" r:id="rId1"/>
     <sheet name="veins-sup" sheetId="2" r:id="rId2"/>
     <sheet name="veins-inf" sheetId="5" r:id="rId3"/>
     <sheet name="PulArt" sheetId="4" r:id="rId4"/>
+    <sheet name="A-V Mapping" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2283" uniqueCount="799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2380" uniqueCount="850">
   <si>
     <t>Filename</t>
   </si>
@@ -2373,30 +2374,15 @@
     <t>Source</t>
   </si>
   <si>
-    <t>veins5, veins0</t>
-  </si>
-  <si>
-    <t>veins_rarm1</t>
-  </si>
-  <si>
     <t>veins_rarm5</t>
   </si>
   <si>
-    <t>veins_larm7</t>
-  </si>
-  <si>
     <t>veins_larm11</t>
   </si>
   <si>
-    <t>liver_veins_hep6</t>
-  </si>
-  <si>
     <t>liver_veins_hep16</t>
   </si>
   <si>
-    <t>liver_veins_hep30</t>
-  </si>
-  <si>
     <t>liver_veins_hep31</t>
   </si>
   <si>
@@ -2421,10 +2407,178 @@
     <t>veins_rleg27</t>
   </si>
   <si>
-    <t>veins_relg27</t>
-  </si>
-  <si>
-    <t>veins19, veins_rleg27, rkidney_veins0, lkidney_veins0, liver_veins_hep6, liver_veins_hep16, liver_veins_hep30, liver_veins_hep31, liver_veins_hep36</t>
+    <t>veins19, veins_rleg27, rkidney_veins0, lkidney_veins0, liver_veins_hep16, liver_veins_hep31, liver_veins_hep36</t>
+  </si>
+  <si>
+    <t>veins3</t>
+  </si>
+  <si>
+    <t>veins7</t>
+  </si>
+  <si>
+    <t>veins_rarm13</t>
+  </si>
+  <si>
+    <t>veins_rarm14</t>
+  </si>
+  <si>
+    <t>veins_larm14</t>
+  </si>
+  <si>
+    <t>veins_larm13</t>
+  </si>
+  <si>
+    <t>veins5, veins0, veins7</t>
+  </si>
+  <si>
+    <t>veins11, veins3</t>
+  </si>
+  <si>
+    <t>veins5, veins7</t>
+  </si>
+  <si>
+    <t>Artery Index</t>
+  </si>
+  <si>
+    <t>Vein Index</t>
+  </si>
+  <si>
+    <t>L Front Head</t>
+  </si>
+  <si>
+    <t>R Back Head</t>
+  </si>
+  <si>
+    <t>R Arm</t>
+  </si>
+  <si>
+    <t>L Back Head</t>
+  </si>
+  <si>
+    <t>Mesenteric Artery</t>
+  </si>
+  <si>
+    <t>L Arm</t>
+  </si>
+  <si>
+    <t>R Kidney</t>
+  </si>
+  <si>
+    <t>L Gastric</t>
+  </si>
+  <si>
+    <t>Splenic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hepatic </t>
+  </si>
+  <si>
+    <t>L Kidney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inferior Mesenteric </t>
+  </si>
+  <si>
+    <t>L Illiac (Upper Leg)</t>
+  </si>
+  <si>
+    <t>R Illiac (Upper Leg)</t>
+  </si>
+  <si>
+    <t>L Leg</t>
+  </si>
+  <si>
+    <t>R Leg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Body Region </t>
+  </si>
+  <si>
+    <t>Supplies/Drains</t>
+  </si>
+  <si>
+    <t>Brain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015_Mynard SuppMaterial </t>
+  </si>
+  <si>
+    <t>Intenstine</t>
+  </si>
+  <si>
+    <t>Stomach</t>
+  </si>
+  <si>
+    <t>Spleen</t>
+  </si>
+  <si>
+    <t>Liver</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>S6</t>
+  </si>
+  <si>
+    <t>S12</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>S15</t>
+  </si>
+  <si>
+    <t>S16</t>
+  </si>
+  <si>
+    <t>S17</t>
+  </si>
+  <si>
+    <t>S18</t>
+  </si>
+  <si>
+    <t>R Head</t>
+  </si>
+  <si>
+    <t>L Head</t>
+  </si>
+  <si>
+    <t>I2</t>
+  </si>
+  <si>
+    <t>I4</t>
+  </si>
+  <si>
+    <t>I6</t>
+  </si>
+  <si>
+    <t>I8</t>
+  </si>
+  <si>
+    <t>I10</t>
+  </si>
+  <si>
+    <t>I16</t>
+  </si>
+  <si>
+    <t>I17</t>
+  </si>
+  <si>
+    <t>I18</t>
+  </si>
+  <si>
+    <t>I19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R Leg </t>
+  </si>
+  <si>
+    <t>veins31</t>
+  </si>
+  <si>
+    <t>veins_rleg16, veins31</t>
   </si>
 </sst>
 </file>
@@ -2446,12 +2600,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2466,8 +2626,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5554,7 +5715,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -5617,10 +5778,10 @@
         <v>695</v>
       </c>
       <c r="D4" t="s">
-        <v>781</v>
+        <v>799</v>
       </c>
       <c r="E4" t="s">
-        <v>696</v>
+        <v>801</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -5631,10 +5792,10 @@
         <v>696</v>
       </c>
       <c r="D5" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="E5" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -5645,10 +5806,10 @@
         <v>697</v>
       </c>
       <c r="D6" t="s">
-        <v>698</v>
+        <v>800</v>
       </c>
       <c r="E6" t="s">
-        <v>698</v>
+        <v>800</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -5659,10 +5820,10 @@
         <v>698</v>
       </c>
       <c r="D7" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="E7" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -5670,7 +5831,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>782</v>
+        <v>793</v>
+      </c>
+      <c r="D8" t="s">
+        <v>795</v>
+      </c>
+      <c r="E8" t="s">
+        <v>795</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
@@ -5678,10 +5845,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>783</v>
+        <v>794</v>
       </c>
       <c r="D9" t="s">
-        <v>782</v>
+        <v>797</v>
+      </c>
+      <c r="E9" t="s">
+        <v>797</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
@@ -5689,7 +5859,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>784</v>
+        <v>781</v>
+      </c>
+      <c r="D10" t="s">
+        <v>796</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
@@ -5697,12 +5870,44 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>785</v>
-      </c>
-      <c r="D11" t="s">
-        <v>784</v>
+        <v>795</v>
       </c>
       <c r="H11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>796</v>
+      </c>
+      <c r="H12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>782</v>
+      </c>
+      <c r="D13" t="s">
+        <v>798</v>
+      </c>
+      <c r="H13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>797</v>
+      </c>
+      <c r="H14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>798</v>
+      </c>
+      <c r="H15" t="s">
         <v>11</v>
       </c>
     </row>
@@ -5714,19 +5919,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E258076-C214-41D6-BCD6-F667F1858984}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="28.140625" customWidth="1"/>
     <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="43.140625" customWidth="1"/>
+    <col min="4" max="4" width="81.28515625" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="6" width="18.140625" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5752,7 +5957,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>775</v>
       </c>
@@ -5760,79 +5965,107 @@
         <v>776</v>
       </c>
       <c r="D2" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="E2" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>791</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>783</v>
+      </c>
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>784</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>785</v>
+      </c>
+      <c r="I5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>787</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="I7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="D8" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="I8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>789</v>
+      </c>
+      <c r="I9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="I10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>793</v>
-      </c>
-      <c r="D10" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>849</v>
+      </c>
+      <c r="I11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+      <c r="D12" t="s">
+        <v>788</v>
+      </c>
+      <c r="I12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>796</v>
-      </c>
-      <c r="D13" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>699</v>
-      </c>
-      <c r="D14" t="s">
-        <v>793</v>
+        <v>848</v>
       </c>
     </row>
   </sheetData>
@@ -10952,4 +11185,401 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{188388E5-F9D8-4148-BF34-9C51095EB628}">
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>802</v>
+      </c>
+      <c r="B1" t="s">
+        <v>803</v>
+      </c>
+      <c r="C1" t="s">
+        <v>820</v>
+      </c>
+      <c r="D1" t="s">
+        <v>821</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>804</v>
+      </c>
+      <c r="D2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>805</v>
+      </c>
+      <c r="D3" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>807</v>
+      </c>
+      <c r="D5" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>808</v>
+      </c>
+      <c r="D8" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>811</v>
+      </c>
+      <c r="D9" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>810</v>
+      </c>
+      <c r="D11" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>812</v>
+      </c>
+      <c r="D12" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>813</v>
+      </c>
+      <c r="D13" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>814</v>
+      </c>
+      <c r="D16" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>32</v>
+      </c>
+      <c r="C17" t="s">
+        <v>815</v>
+      </c>
+      <c r="D17" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>42</v>
+      </c>
+      <c r="C21" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>45</v>
+      </c>
+      <c r="C24" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>46</v>
+      </c>
+      <c r="C25" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>828</v>
+      </c>
+      <c r="C26" t="s">
+        <v>836</v>
+      </c>
+      <c r="D26" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>829</v>
+      </c>
+      <c r="C27" t="s">
+        <v>837</v>
+      </c>
+      <c r="D27" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>830</v>
+      </c>
+      <c r="C28" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>831</v>
+      </c>
+      <c r="C29" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>832</v>
+      </c>
+      <c r="C30" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>833</v>
+      </c>
+      <c r="C31" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>834</v>
+      </c>
+      <c r="C32" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>835</v>
+      </c>
+      <c r="C33" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>838</v>
+      </c>
+      <c r="C34" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>839</v>
+      </c>
+      <c r="C35" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>840</v>
+      </c>
+      <c r="C36" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>841</v>
+      </c>
+      <c r="C37" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>842</v>
+      </c>
+      <c r="C38" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>843</v>
+      </c>
+      <c r="C39" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>844</v>
+      </c>
+      <c r="C40" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>845</v>
+      </c>
+      <c r="C41" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>846</v>
+      </c>
+      <c r="C42" t="s">
+        <v>818</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/FlowTracker.xlsx
+++ b/FlowTracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E42B821-236F-48BB-99C7-5A484EDEB984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FA70EC-6427-4046-8F80-A1BDD186CBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21697" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21697" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="arteries" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2380" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="862">
   <si>
     <t>Filename</t>
   </si>
@@ -2503,9 +2503,6 @@
     <t xml:space="preserve">2015_Mynard SuppMaterial </t>
   </si>
   <si>
-    <t>Intenstine</t>
-  </si>
-  <si>
     <t>Stomach</t>
   </si>
   <si>
@@ -2560,9 +2557,6 @@
     <t>I10</t>
   </si>
   <si>
-    <t>I16</t>
-  </si>
-  <si>
     <t>I17</t>
   </si>
   <si>
@@ -2572,13 +2566,55 @@
     <t>I19</t>
   </si>
   <si>
-    <t xml:space="preserve">R Leg </t>
-  </si>
-  <si>
     <t>veins31</t>
   </si>
   <si>
-    <t>veins_rleg16, veins31</t>
+    <t>veins31, veins_rleg16</t>
+  </si>
+  <si>
+    <t>I14</t>
+  </si>
+  <si>
+    <t>I20</t>
+  </si>
+  <si>
+    <t>I21</t>
+  </si>
+  <si>
+    <t>S Intenstines and pancreas</t>
+  </si>
+  <si>
+    <t>L Intenstine</t>
+  </si>
+  <si>
+    <t>1996_Legget Dwell Time Organs</t>
+  </si>
+  <si>
+    <t>Total Blood Volume (ml) 1996_legget</t>
+  </si>
+  <si>
+    <t>5300 mL</t>
+  </si>
+  <si>
+    <t>Caridac Output (mL/min) 1996_Legget</t>
+  </si>
+  <si>
+    <t>6500 ml/min</t>
+  </si>
+  <si>
+    <t>% Total BV</t>
+  </si>
+  <si>
+    <t>% CO Recived</t>
+  </si>
+  <si>
+    <t>3.8, 0.6</t>
+  </si>
+  <si>
+    <t>10, 1</t>
+  </si>
+  <si>
+    <t>25.5 (total)</t>
   </si>
 </sst>
 </file>
@@ -2600,7 +2636,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2613,11 +2649,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -2626,9 +2683,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5922,10 +5985,10 @@
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="28.140625" customWidth="1"/>
     <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="81.28515625" customWidth="1"/>
+    <col min="4" max="4" width="119.5703125" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="6" width="18.140625" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" customWidth="1"/>
@@ -6016,10 +6079,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>699</v>
+      </c>
+      <c r="D8" t="s">
         <v>788</v>
-      </c>
-      <c r="D8" t="s">
-        <v>789</v>
       </c>
       <c r="I8" t="s">
         <v>11</v>
@@ -6027,6 +6090,9 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>788</v>
+      </c>
+      <c r="D9" t="s">
         <v>789</v>
       </c>
       <c r="I9" t="s">
@@ -6035,7 +6101,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>790</v>
+        <v>845</v>
       </c>
       <c r="I10" t="s">
         <v>11</v>
@@ -6043,10 +6109,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>791</v>
-      </c>
-      <c r="D11" t="s">
-        <v>849</v>
+        <v>789</v>
       </c>
       <c r="I11" t="s">
         <v>11</v>
@@ -6054,18 +6117,15 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>699</v>
-      </c>
-      <c r="D12" t="s">
-        <v>788</v>
-      </c>
-      <c r="I12" t="s">
-        <v>11</v>
+        <v>790</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>848</v>
+        <v>791</v>
+      </c>
+      <c r="D13" t="s">
+        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -11189,16 +11249,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{188388E5-F9D8-4148-BF34-9C51095EB628}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="18.42578125" customWidth="1"/>
     <col min="3" max="3" width="23.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" customWidth="1"/>
+    <col min="5" max="5" width="36.7109375" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>802</v>
       </c>
@@ -11208,375 +11272,536 @@
       <c r="C1" t="s">
         <v>820</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="7" t="s">
         <v>821</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
       <c r="C2" t="s">
         <v>804</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="7" t="s">
         <v>822</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E2" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="F2" s="5">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>805</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="7" t="s">
         <v>822</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E3" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="F3" s="5">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9</v>
       </c>
       <c r="C4" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D4" s="7"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="3" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>807</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="7" t="s">
         <v>822</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E5" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="F5" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D6" s="7"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D7" s="7"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>808</v>
       </c>
-      <c r="D8" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D8" s="7" t="s">
+        <v>850</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>859</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>20</v>
       </c>
       <c r="C9" t="s">
         <v>811</v>
       </c>
-      <c r="D9" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>21</v>
       </c>
       <c r="C10" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="7"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>24</v>
       </c>
       <c r="C11" t="s">
         <v>810</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="7" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E11" s="6">
+        <v>2</v>
+      </c>
+      <c r="F11" s="6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>25</v>
       </c>
       <c r="C12" t="s">
         <v>812</v>
       </c>
-      <c r="D12" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D12" s="7" t="s">
+        <v>825</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="F12" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26</v>
       </c>
       <c r="C13" t="s">
         <v>813</v>
       </c>
-      <c r="D13" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D13" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="E13" s="6">
+        <v>10</v>
+      </c>
+      <c r="F13" s="6">
+        <v>6.5</v>
+      </c>
+      <c r="I13" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>27</v>
       </c>
       <c r="C14" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D14" s="7"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>28</v>
       </c>
       <c r="C15" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D15" s="7"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>30</v>
       </c>
       <c r="C16" t="s">
         <v>814</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="7" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="5">
+        <v>2</v>
+      </c>
+      <c r="F16" s="5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>32</v>
       </c>
       <c r="C17" t="s">
         <v>815</v>
       </c>
-      <c r="D17" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D17" s="7" t="s">
+        <v>851</v>
+      </c>
+      <c r="E17" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F17" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>35</v>
       </c>
       <c r="C18" t="s">
         <v>816</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D18" s="7"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>37</v>
       </c>
       <c r="C19" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D19" s="7"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>40</v>
       </c>
       <c r="C20" t="s">
         <v>818</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D20" s="7"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>42</v>
       </c>
       <c r="C21" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D21" s="7"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>43</v>
       </c>
       <c r="C22" t="s">
         <v>818</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D22" s="7"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>818</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D23" s="7"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D24" s="7"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>46</v>
       </c>
       <c r="C25" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D25" s="7"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C26" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D26" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C27" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D27" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C28" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C29" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C30" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C31" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C32" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C33" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
+        <v>837</v>
+      </c>
+      <c r="C34" t="s">
+        <v>826</v>
+      </c>
+      <c r="D34" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
         <v>838</v>
       </c>
-      <c r="C34" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
+      <c r="C35" t="s">
+        <v>826</v>
+      </c>
+      <c r="D35" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
         <v>839</v>
       </c>
-      <c r="C35" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
+      <c r="C36" t="s">
+        <v>826</v>
+      </c>
+      <c r="D36" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
         <v>840</v>
-      </c>
-      <c r="C36" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>841</v>
       </c>
       <c r="C37" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C38" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
+        <v>847</v>
+      </c>
+      <c r="C39" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>842</v>
+      </c>
+      <c r="C40" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
         <v>843</v>
-      </c>
-      <c r="C39" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>844</v>
-      </c>
-      <c r="C40" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" t="s">
-        <v>845</v>
       </c>
       <c r="C41" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C42" t="s">
         <v>818</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>848</v>
+      </c>
+      <c r="C43" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>849</v>
+      </c>
+      <c r="C44" t="s">
+        <v>819</v>
       </c>
     </row>
   </sheetData>

--- a/FlowTracker.xlsx
+++ b/FlowTracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\PHSAhome2.phsabc.ehcnet.ca\Cassidy.Northway\Remote Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FA70EC-6427-4046-8F80-A1BDD186CBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE0B03A2-17C1-49EB-B3DA-3FF6E79BC826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21697" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4770" windowWidth="18240" windowHeight="28440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="arteries" sheetId="1" r:id="rId1"/>
@@ -18,18 +18,30 @@
     <sheet name="veins-inf" sheetId="5" r:id="rId3"/>
     <sheet name="PulArt" sheetId="4" r:id="rId4"/>
     <sheet name="A-V Mapping" sheetId="6" r:id="rId5"/>
+    <sheet name="Dwell Time Calcs" sheetId="7" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2410" uniqueCount="867">
   <si>
     <t>Filename</t>
   </si>
@@ -2500,9 +2512,6 @@
     <t>Brain</t>
   </si>
   <si>
-    <t xml:space="preserve">2015_Mynard SuppMaterial </t>
-  </si>
-  <si>
     <t>Stomach</t>
   </si>
   <si>
@@ -2587,41 +2596,59 @@
     <t>L Intenstine</t>
   </si>
   <si>
-    <t>1996_Legget Dwell Time Organs</t>
-  </si>
-  <si>
-    <t>Total Blood Volume (ml) 1996_legget</t>
-  </si>
-  <si>
-    <t>5300 mL</t>
-  </si>
-  <si>
-    <t>Caridac Output (mL/min) 1996_Legget</t>
-  </si>
-  <si>
-    <t>6500 ml/min</t>
-  </si>
-  <si>
-    <t>% Total BV</t>
-  </si>
-  <si>
-    <t>% CO Recived</t>
-  </si>
-  <si>
-    <t>3.8, 0.6</t>
-  </si>
-  <si>
-    <t>10, 1</t>
-  </si>
-  <si>
-    <t>25.5 (total)</t>
+    <t>Organ</t>
+  </si>
+  <si>
+    <t>S Intestines</t>
+  </si>
+  <si>
+    <t>Pancreas</t>
+  </si>
+  <si>
+    <t>L Intestines</t>
+  </si>
+  <si>
+    <t>Liver (From organs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liver </t>
+  </si>
+  <si>
+    <t>% Total Blood Volume</t>
+  </si>
+  <si>
+    <t>%  of Cardiac Output</t>
+  </si>
+  <si>
+    <t>Total BV (mL)</t>
+  </si>
+  <si>
+    <t>Cardiac Output (mL/min)</t>
+  </si>
+  <si>
+    <t>1996_legget</t>
+  </si>
+  <si>
+    <t>Dwell Time (A&gt;O&gt;V) (min)</t>
+  </si>
+  <si>
+    <t>Dwell Time (s)</t>
+  </si>
+  <si>
+    <t>ICRP 89</t>
+  </si>
+  <si>
+    <t>2010_Eipel</t>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2635,8 +2662,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2645,19 +2678,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2686,12 +2725,12 @@
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2739,9 +2778,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2779,7 +2818,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2885,7 +2924,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3027,7 +3066,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6101,7 +6140,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="I10" t="s">
         <v>11</v>
@@ -6125,7 +6164,7 @@
         <v>791</v>
       </c>
       <c r="D13" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
   </sheetData>
@@ -11249,562 +11288,1123 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{188388E5-F9D8-4148-BF34-9C51095EB628}">
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:U44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" customWidth="1"/>
-    <col min="5" max="5" width="36.7109375" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="27" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" customWidth="1"/>
+    <col min="6" max="6" width="36.7109375" customWidth="1"/>
+    <col min="7" max="7" width="26.5703125" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>866</v>
+      </c>
+      <c r="B1" t="s">
         <v>802</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>803</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>820</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="4" t="s">
         <v>821</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>857</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>858</v>
-      </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="2" t="s">
-        <v>853</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>804</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>805</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>806</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>807</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>806</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>806</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>808</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>811</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>823</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>804</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>809</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>810</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>812</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>813</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
+        <v>809</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>809</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>814</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s">
+        <v>815</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>816</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>37</v>
+      </c>
+      <c r="D19" t="s">
+        <v>817</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+    </row>
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>40</v>
+      </c>
+      <c r="D20" t="s">
+        <v>818</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+    </row>
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>42</v>
+      </c>
+      <c r="D21" t="s">
+        <v>819</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>43</v>
+      </c>
+      <c r="D22" t="s">
+        <v>818</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+    </row>
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>44</v>
+      </c>
+      <c r="D23" t="s">
+        <v>818</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+    </row>
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>45</v>
+      </c>
+      <c r="D24" t="s">
+        <v>819</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+    </row>
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>46</v>
+      </c>
+      <c r="D25" t="s">
+        <v>819</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+    </row>
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>826</v>
+      </c>
+      <c r="D26" t="s">
+        <v>834</v>
+      </c>
+      <c r="E26" t="s">
         <v>822</v>
       </c>
-      <c r="E2" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="F2" s="5">
-        <v>12</v>
-      </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="2" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>805</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+    </row>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>827</v>
+      </c>
+      <c r="D27" t="s">
+        <v>835</v>
+      </c>
+      <c r="E27" t="s">
         <v>822</v>
       </c>
-      <c r="E3" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="F3" s="5">
-        <v>12</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="3" t="s">
-        <v>855</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>828</v>
+      </c>
+      <c r="D28" t="s">
         <v>806</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="3" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>807</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>822</v>
-      </c>
-      <c r="E5" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="F5" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>829</v>
+      </c>
+      <c r="D29" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>830</v>
+      </c>
+      <c r="D30" t="s">
         <v>806</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>831</v>
+      </c>
+      <c r="D31" t="s">
         <v>806</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>808</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>850</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>859</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>811</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>824</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>832</v>
+      </c>
+      <c r="D32" t="s">
         <v>809</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>810</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>810</v>
-      </c>
-      <c r="E11" s="6">
-        <v>2</v>
-      </c>
-      <c r="F11" s="6">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>812</v>
-      </c>
-      <c r="D12" s="7" t="s">
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>833</v>
+      </c>
+      <c r="D33" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>836</v>
+      </c>
+      <c r="D34" t="s">
         <v>825</v>
       </c>
-      <c r="E12" s="6">
-        <v>1.4</v>
-      </c>
-      <c r="F12" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>813</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>826</v>
-      </c>
-      <c r="E13" s="6">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6">
-        <v>6.5</v>
-      </c>
-      <c r="I13" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>809</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>809</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>814</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>814</v>
-      </c>
-      <c r="E16" s="5">
-        <v>2</v>
-      </c>
-      <c r="F16" s="5">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>32</v>
-      </c>
-      <c r="C17" t="s">
-        <v>815</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>851</v>
-      </c>
-      <c r="E17" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="F17" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>816</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>817</v>
-      </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>40</v>
-      </c>
-      <c r="C20" t="s">
-        <v>818</v>
-      </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>42</v>
-      </c>
-      <c r="C21" t="s">
-        <v>819</v>
-      </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>43</v>
-      </c>
-      <c r="C22" t="s">
-        <v>818</v>
-      </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>44</v>
-      </c>
-      <c r="C23" t="s">
-        <v>818</v>
-      </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>45</v>
-      </c>
-      <c r="C24" t="s">
-        <v>819</v>
-      </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>46</v>
-      </c>
-      <c r="C25" t="s">
-        <v>819</v>
-      </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>827</v>
-      </c>
-      <c r="C26" t="s">
-        <v>835</v>
-      </c>
-      <c r="D26" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>828</v>
-      </c>
-      <c r="C27" t="s">
-        <v>836</v>
-      </c>
-      <c r="D27" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>829</v>
-      </c>
-      <c r="C28" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>830</v>
-      </c>
-      <c r="C29" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>831</v>
-      </c>
-      <c r="C30" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>832</v>
-      </c>
-      <c r="C31" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>833</v>
-      </c>
-      <c r="C32" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>834</v>
-      </c>
-      <c r="C33" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
+      <c r="E34" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
         <v>837</v>
       </c>
-      <c r="C34" t="s">
-        <v>826</v>
-      </c>
-      <c r="D34" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
+      <c r="D35" t="s">
+        <v>825</v>
+      </c>
+      <c r="E35" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
         <v>838</v>
       </c>
-      <c r="C35" t="s">
-        <v>826</v>
-      </c>
-      <c r="D35" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
+      <c r="D36" t="s">
+        <v>825</v>
+      </c>
+      <c r="E36" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
         <v>839</v>
-      </c>
-      <c r="C36" t="s">
-        <v>826</v>
-      </c>
-      <c r="D36" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>840</v>
-      </c>
-      <c r="C37" t="s">
-        <v>814</v>
       </c>
       <c r="D37" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>841</v>
-      </c>
+      <c r="E37" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
-        <v>810</v>
+        <v>840</v>
       </c>
       <c r="D38" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
+      <c r="E38" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>846</v>
+      </c>
+      <c r="D39" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="40" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>841</v>
+      </c>
+      <c r="D40" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>842</v>
+      </c>
+      <c r="D41" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="42" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C42" t="s">
+        <v>843</v>
+      </c>
+      <c r="D42" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
         <v>847</v>
       </c>
-      <c r="C39" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>842</v>
-      </c>
-      <c r="C40" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B41" t="s">
-        <v>843</v>
-      </c>
-      <c r="C41" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
-        <v>844</v>
-      </c>
-      <c r="C42" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B43" t="s">
+      <c r="D43" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="44" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C44" t="s">
         <v>848</v>
       </c>
-      <c r="C43" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
-        <v>849</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>819</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F665A280-B941-4509-8B0A-1E2E1E43C816}">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="39.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" customWidth="1"/>
+    <col min="4" max="4" width="30.140625" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="23.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B2">
+        <v>1.2</v>
+      </c>
+      <c r="C2">
+        <v>12</v>
+      </c>
+      <c r="D2">
+        <f>($F$2*B2)/($G$2*C2)</f>
+        <v>8.1538461538461532E-2</v>
+      </c>
+      <c r="E2" s="7">
+        <f>D2*60</f>
+        <v>4.8923076923076918</v>
+      </c>
+      <c r="F2">
+        <v>5300</v>
+      </c>
+      <c r="G2">
+        <v>6500</v>
+      </c>
+      <c r="I2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>852</v>
+      </c>
+      <c r="B3">
+        <v>3.8</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D11" si="0">($F$2*B3)/($G$2*C3)</f>
+        <v>0.30984615384615383</v>
+      </c>
+      <c r="E3" s="7">
+        <f>D3*60 +E11</f>
+        <v>37.902510121457489</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>853</v>
+      </c>
+      <c r="B4">
+        <v>0.6</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>0.48923076923076925</v>
+      </c>
+      <c r="E4" s="7">
+        <f>D4*60</f>
+        <v>29.353846153846156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>823</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>0.81538461538461537</v>
+      </c>
+      <c r="E5" s="7">
+        <f>D5*60 +E11</f>
+        <v>68.234817813765176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>810</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>8.5829959514170037E-2</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" ref="E3:E11" si="1">D6*60</f>
+        <v>5.1497975708502022</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>824</v>
+      </c>
+      <c r="B7">
+        <v>1.4</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>0.38051282051282048</v>
+      </c>
+      <c r="E7" s="7">
+        <f>D7*60+E11</f>
+        <v>42.142510121457491</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>854</v>
+      </c>
+      <c r="B8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>0.44846153846153852</v>
+      </c>
+      <c r="E8" s="7">
+        <f>D8*60 + E11</f>
+        <v>46.219433198380571</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>814</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>19</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>8.5829959514170037E-2</v>
+      </c>
+      <c r="E9" s="7">
+        <f t="shared" si="1"/>
+        <v>5.1497975708502022</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>856</v>
+      </c>
+      <c r="B10">
+        <f>10/4</f>
+        <v>2.5</v>
+      </c>
+      <c r="C10">
+        <v>6.5</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>0.31360946745562129</v>
+      </c>
+      <c r="E10" s="7">
+        <f t="shared" si="1"/>
+        <v>18.816568047337277</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>855</v>
+      </c>
+      <c r="B11">
+        <f>3*10/4</f>
+        <v>7.5</v>
+      </c>
+      <c r="C11">
+        <f>25.5-6.5</f>
+        <v>19</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>0.32186234817813764</v>
+      </c>
+      <c r="E11" s="7">
+        <f t="shared" si="1"/>
+        <v>19.311740890688259</v>
+      </c>
+      <c r="I11" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/FlowTracker.xlsx
+++ b/FlowTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46257476-5D13-4CE3-A2A4-04C9D95340FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF2329E-AAE3-4721-8746-92FC78FBE3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3186,9 +3186,6 @@
     <t>2;82;85;0;4.89</t>
   </si>
   <si>
-    <t>0;126;126;0;1</t>
-  </si>
-  <si>
     <t>1;28;28;0;1</t>
   </si>
   <si>
@@ -3562,6 +3559,9 @@
   </si>
   <si>
     <t>126;98;99;0;0</t>
+  </si>
+  <si>
+    <t>0;126;126;0;0.955</t>
   </si>
 </sst>
 </file>
@@ -4013,7 +4013,7 @@
         <v>936</v>
       </c>
       <c r="B2" t="s">
-        <v>1047</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
@@ -4021,7 +4021,7 @@
         <v>935</v>
       </c>
       <c r="B3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
@@ -4037,7 +4037,7 @@
         <v>844</v>
       </c>
       <c r="B5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
@@ -4045,7 +4045,7 @@
         <v>845</v>
       </c>
       <c r="B6" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
@@ -4053,7 +4053,7 @@
         <v>818</v>
       </c>
       <c r="B7" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
@@ -4061,7 +4061,7 @@
         <v>807</v>
       </c>
       <c r="B8" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
@@ -4069,7 +4069,7 @@
         <v>819</v>
       </c>
       <c r="B9" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
@@ -4077,7 +4077,7 @@
         <v>846</v>
       </c>
       <c r="B10" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
@@ -4085,7 +4085,7 @@
         <v>811</v>
       </c>
       <c r="B11" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
@@ -4093,7 +4093,7 @@
         <v>848</v>
       </c>
       <c r="B12" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
@@ -4101,7 +4101,7 @@
         <v>847</v>
       </c>
       <c r="B13" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
@@ -4109,7 +4109,7 @@
         <v>1007</v>
       </c>
       <c r="B14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
@@ -4117,7 +4117,7 @@
         <v>1008</v>
       </c>
       <c r="B15" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
@@ -4125,7 +4125,7 @@
         <v>1009</v>
       </c>
       <c r="B16" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
@@ -4133,7 +4133,7 @@
         <v>1010</v>
       </c>
       <c r="B17" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
@@ -4141,7 +4141,7 @@
         <v>1022</v>
       </c>
       <c r="B18" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
@@ -4149,7 +4149,7 @@
         <v>1011</v>
       </c>
       <c r="B19" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
@@ -4157,7 +4157,7 @@
         <v>1014</v>
       </c>
       <c r="B20" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
@@ -4165,7 +4165,7 @@
         <v>1015</v>
       </c>
       <c r="B21" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
@@ -4173,7 +4173,7 @@
         <v>1016</v>
       </c>
       <c r="B22" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
@@ -4181,7 +4181,7 @@
         <v>1017</v>
       </c>
       <c r="B23" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
@@ -4189,7 +4189,7 @@
         <v>1018</v>
       </c>
       <c r="B24" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
@@ -4197,7 +4197,7 @@
         <v>1019</v>
       </c>
       <c r="B25" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
@@ -4205,7 +4205,7 @@
         <v>1020</v>
       </c>
       <c r="B26" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
@@ -4213,7 +4213,7 @@
         <v>1021</v>
       </c>
       <c r="B27" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
@@ -4221,7 +4221,7 @@
         <v>1012</v>
       </c>
       <c r="B28" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
@@ -4229,7 +4229,7 @@
         <v>1013</v>
       </c>
       <c r="B29" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
@@ -4237,7 +4237,7 @@
         <v>963</v>
       </c>
       <c r="B30" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
@@ -4245,7 +4245,7 @@
         <v>964</v>
       </c>
       <c r="B31" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
@@ -4253,7 +4253,7 @@
         <v>965</v>
       </c>
       <c r="B32" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
@@ -4261,7 +4261,7 @@
         <v>966</v>
       </c>
       <c r="B33" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
@@ -4269,7 +4269,7 @@
         <v>967</v>
       </c>
       <c r="B34" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
@@ -4277,7 +4277,7 @@
         <v>968</v>
       </c>
       <c r="B35" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
@@ -4285,7 +4285,7 @@
         <v>969</v>
       </c>
       <c r="B36" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.45">
@@ -4293,7 +4293,7 @@
         <v>970</v>
       </c>
       <c r="B37" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
@@ -4301,7 +4301,7 @@
         <v>971</v>
       </c>
       <c r="B38" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
@@ -4309,7 +4309,7 @@
         <v>972</v>
       </c>
       <c r="B39" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
@@ -4317,7 +4317,7 @@
         <v>973</v>
       </c>
       <c r="B40" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
@@ -4325,7 +4325,7 @@
         <v>974</v>
       </c>
       <c r="B41" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.45">
@@ -4333,7 +4333,7 @@
         <v>975</v>
       </c>
       <c r="B42" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.45">
@@ -4341,7 +4341,7 @@
         <v>976</v>
       </c>
       <c r="B43" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.45">
@@ -4349,7 +4349,7 @@
         <v>977</v>
       </c>
       <c r="B44" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
@@ -4357,7 +4357,7 @@
         <v>978</v>
       </c>
       <c r="B45" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
@@ -4365,7 +4365,7 @@
         <v>979</v>
       </c>
       <c r="B46" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.45">
@@ -4373,7 +4373,7 @@
         <v>980</v>
       </c>
       <c r="B47" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.45">
@@ -4381,7 +4381,7 @@
         <v>981</v>
       </c>
       <c r="B48" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.45">
@@ -4389,7 +4389,7 @@
         <v>982</v>
       </c>
       <c r="B49" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.45">
@@ -4397,7 +4397,7 @@
         <v>983</v>
       </c>
       <c r="B50" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.45">
@@ -4405,7 +4405,7 @@
         <v>984</v>
       </c>
       <c r="B51" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.45">
@@ -4413,7 +4413,7 @@
         <v>985</v>
       </c>
       <c r="B52" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.45">
@@ -4421,7 +4421,7 @@
         <v>986</v>
       </c>
       <c r="B53" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.45">
@@ -4429,7 +4429,7 @@
         <v>987</v>
       </c>
       <c r="B54" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.45">
@@ -4437,7 +4437,7 @@
         <v>937</v>
       </c>
       <c r="B55" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.45">
@@ -4445,7 +4445,7 @@
         <v>938</v>
       </c>
       <c r="B56" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.45">
@@ -4453,7 +4453,7 @@
         <v>939</v>
       </c>
       <c r="B57" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.45">
@@ -4461,7 +4461,7 @@
         <v>940</v>
       </c>
       <c r="B58" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.45">
@@ -4469,7 +4469,7 @@
         <v>941</v>
       </c>
       <c r="B59" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.45">
@@ -4477,7 +4477,7 @@
         <v>942</v>
       </c>
       <c r="B60" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.45">
@@ -4485,7 +4485,7 @@
         <v>943</v>
       </c>
       <c r="B61" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.45">
@@ -4493,7 +4493,7 @@
         <v>944</v>
       </c>
       <c r="B62" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.45">
@@ -4501,7 +4501,7 @@
         <v>945</v>
       </c>
       <c r="B63" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.45">
@@ -4509,7 +4509,7 @@
         <v>946</v>
       </c>
       <c r="B64" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.45">
@@ -4517,7 +4517,7 @@
         <v>947</v>
       </c>
       <c r="B65" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.45">
@@ -4525,7 +4525,7 @@
         <v>948</v>
       </c>
       <c r="B66" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.45">
@@ -4533,7 +4533,7 @@
         <v>949</v>
       </c>
       <c r="B67" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.45">
@@ -4541,7 +4541,7 @@
         <v>950</v>
       </c>
       <c r="B68" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.45">
@@ -4549,7 +4549,7 @@
         <v>951</v>
       </c>
       <c r="B69" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.45">
@@ -4557,7 +4557,7 @@
         <v>952</v>
       </c>
       <c r="B70" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.45">
@@ -4565,7 +4565,7 @@
         <v>953</v>
       </c>
       <c r="B71" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.45">
@@ -4573,7 +4573,7 @@
         <v>954</v>
       </c>
       <c r="B72" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.45">
@@ -4581,7 +4581,7 @@
         <v>955</v>
       </c>
       <c r="B73" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.45">
@@ -4589,7 +4589,7 @@
         <v>956</v>
       </c>
       <c r="B74" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.45">
@@ -4597,7 +4597,7 @@
         <v>957</v>
       </c>
       <c r="B75" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.45">
@@ -4605,7 +4605,7 @@
         <v>958</v>
       </c>
       <c r="B76" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.45">
@@ -4613,7 +4613,7 @@
         <v>959</v>
       </c>
       <c r="B77" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.45">
@@ -4621,7 +4621,7 @@
         <v>960</v>
       </c>
       <c r="B78" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.45">
@@ -4629,7 +4629,7 @@
         <v>961</v>
       </c>
       <c r="B79" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.45">
@@ -4637,7 +4637,7 @@
         <v>962</v>
       </c>
       <c r="B80" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.45">
@@ -4645,7 +4645,7 @@
         <v>988</v>
       </c>
       <c r="B81" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.45">
@@ -4653,7 +4653,7 @@
         <v>989</v>
       </c>
       <c r="B82" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.45">
@@ -4661,7 +4661,7 @@
         <v>990</v>
       </c>
       <c r="B83" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.45">
@@ -4669,7 +4669,7 @@
         <v>991</v>
       </c>
       <c r="B84" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.45">
@@ -4677,7 +4677,7 @@
         <v>992</v>
       </c>
       <c r="B85" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.45">
@@ -4685,7 +4685,7 @@
         <v>993</v>
       </c>
       <c r="B86" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.45">
@@ -4693,7 +4693,7 @@
         <v>994</v>
       </c>
       <c r="B87" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.45">
@@ -4701,7 +4701,7 @@
         <v>995</v>
       </c>
       <c r="B88" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.45">
@@ -4709,7 +4709,7 @@
         <v>996</v>
       </c>
       <c r="B89" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.45">
@@ -4717,7 +4717,7 @@
         <v>997</v>
       </c>
       <c r="B90" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.45">
@@ -4725,7 +4725,7 @@
         <v>998</v>
       </c>
       <c r="B91" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.45">
@@ -4733,7 +4733,7 @@
         <v>999</v>
       </c>
       <c r="B92" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.45">
@@ -4741,7 +4741,7 @@
         <v>1000</v>
       </c>
       <c r="B93" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.45">
@@ -4749,7 +4749,7 @@
         <v>1001</v>
       </c>
       <c r="B94" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.45">
@@ -4757,7 +4757,7 @@
         <v>1002</v>
       </c>
       <c r="B95" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.45">
@@ -4765,7 +4765,7 @@
         <v>1003</v>
       </c>
       <c r="B96" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.45">
@@ -4773,7 +4773,7 @@
         <v>1004</v>
       </c>
       <c r="B97" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.45">
@@ -4781,7 +4781,7 @@
         <v>1005</v>
       </c>
       <c r="B98" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.45">
@@ -4789,7 +4789,7 @@
         <v>1006</v>
       </c>
       <c r="B99" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.45">
@@ -4797,7 +4797,7 @@
         <v>140</v>
       </c>
       <c r="B100" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.45">
@@ -4805,7 +4805,7 @@
         <v>927</v>
       </c>
       <c r="B101" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.45">
@@ -4813,7 +4813,7 @@
         <v>928</v>
       </c>
       <c r="B102" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.45">
@@ -4821,7 +4821,7 @@
         <v>929</v>
       </c>
       <c r="B103" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.45">
@@ -4829,7 +4829,7 @@
         <v>930</v>
       </c>
       <c r="B104" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.45">
@@ -4837,7 +4837,7 @@
         <v>931</v>
       </c>
       <c r="B105" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.45">
@@ -4845,7 +4845,7 @@
         <v>1023</v>
       </c>
       <c r="B106" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.45">
@@ -4853,7 +4853,7 @@
         <v>1024</v>
       </c>
       <c r="B107" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.45">
@@ -4861,7 +4861,7 @@
         <v>1025</v>
       </c>
       <c r="B108" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.45">
@@ -4869,7 +4869,7 @@
         <v>1026</v>
       </c>
       <c r="B109" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.45">
@@ -4877,7 +4877,7 @@
         <v>1027</v>
       </c>
       <c r="B110" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.45">
@@ -4885,7 +4885,7 @@
         <v>1028</v>
       </c>
       <c r="B111" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.45">
@@ -4893,7 +4893,7 @@
         <v>1029</v>
       </c>
       <c r="B112" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.45">
@@ -4901,7 +4901,7 @@
         <v>1030</v>
       </c>
       <c r="B113" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.45">
@@ -4909,7 +4909,7 @@
         <v>1031</v>
       </c>
       <c r="B114" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.45">
@@ -4917,7 +4917,7 @@
         <v>1032</v>
       </c>
       <c r="B115" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.45">
@@ -4925,7 +4925,7 @@
         <v>1033</v>
       </c>
       <c r="B116" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.45">
@@ -4933,7 +4933,7 @@
         <v>1034</v>
       </c>
       <c r="B117" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.45">
@@ -4941,7 +4941,7 @@
         <v>1035</v>
       </c>
       <c r="B118" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.45">
@@ -4949,7 +4949,7 @@
         <v>1036</v>
       </c>
       <c r="B119" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.45">
@@ -4957,7 +4957,7 @@
         <v>1037</v>
       </c>
       <c r="B120" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.45">
@@ -4965,7 +4965,7 @@
         <v>1038</v>
       </c>
       <c r="B121" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.45">
@@ -4973,7 +4973,7 @@
         <v>1039</v>
       </c>
       <c r="B122" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.45">
@@ -4981,7 +4981,7 @@
         <v>1040</v>
       </c>
       <c r="B123" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.45">
@@ -4989,7 +4989,7 @@
         <v>1041</v>
       </c>
       <c r="B124" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.45">
@@ -4997,7 +4997,7 @@
         <v>1042</v>
       </c>
       <c r="B125" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.45">
@@ -5005,7 +5005,7 @@
         <v>1043</v>
       </c>
       <c r="B126" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.45">
@@ -5013,7 +5013,7 @@
         <v>1044</v>
       </c>
       <c r="B127" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.45">
@@ -5021,7 +5021,7 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
   </sheetData>

--- a/FlowTracker.xlsx
+++ b/FlowTracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF2329E-AAE3-4721-8746-92FC78FBE3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A85CAB-2A17-4317-A213-FE266235E01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,6 +23,7 @@
     <sheet name="PulmArtOld" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -3180,388 +3181,388 @@
     <t>arteries_rleg23_0</t>
   </si>
   <si>
-    <t>LocationIDNumber;OutFlowA;OutFlowB;OutFlowC;DwellTime(s);</t>
-  </si>
-  <si>
-    <t>2;82;85;0;4.89</t>
-  </si>
-  <si>
-    <t>1;28;28;0;1</t>
-  </si>
-  <si>
-    <t>3;11;11;0;37.90</t>
-  </si>
-  <si>
-    <t>4;11;11;0;29.35</t>
-  </si>
-  <si>
-    <t>5;11;11;0;68.23</t>
-  </si>
-  <si>
-    <t>6;63;63;0;5.15</t>
-  </si>
-  <si>
-    <t>7;11;11;0;42.14</t>
-  </si>
-  <si>
-    <t>8;11;11;0;46.22</t>
-  </si>
-  <si>
-    <t>9;61;61;0;5.15</t>
-  </si>
-  <si>
-    <t>10;55;57;59;18.82</t>
-  </si>
-  <si>
-    <t>11;55;57;59;19.31</t>
-  </si>
-  <si>
-    <t>12;96;96;0;17.89</t>
-  </si>
-  <si>
-    <t>13;97;97;0;17.89</t>
-  </si>
-  <si>
-    <t>14;93;93;0;17.89</t>
-  </si>
-  <si>
-    <t>15;94;94;0;17.89</t>
-  </si>
-  <si>
-    <t>16;95;95;0;17.89</t>
-  </si>
-  <si>
-    <t>17;91;91;0;17.89</t>
-  </si>
-  <si>
-    <t>18;67;67;0;39.92</t>
-  </si>
-  <si>
-    <t>19;72;72;0;39.92</t>
-  </si>
-  <si>
-    <t>20;76;76;0;39.92</t>
-  </si>
-  <si>
-    <t>21;75;75;0;39.92</t>
-  </si>
-  <si>
-    <t>22;70;70;0;39.92</t>
-  </si>
-  <si>
-    <t>23;74;74;0;39.92</t>
-  </si>
-  <si>
-    <t>24;78;78;0;39.92</t>
-  </si>
-  <si>
-    <t>25;77;77;0;39.92</t>
-  </si>
-  <si>
-    <t>26;100;103;0;5.14</t>
-  </si>
-  <si>
-    <t>27;101;102;0;5.14</t>
-  </si>
-  <si>
-    <t>28;29;30;0;0</t>
-  </si>
-  <si>
-    <t>29;31;32;0;0</t>
-  </si>
-  <si>
-    <t>30;33;34;0;0</t>
-  </si>
-  <si>
-    <t>31;35;36;0;0</t>
-  </si>
-  <si>
-    <t>32;2;2;0;0</t>
-  </si>
-  <si>
-    <t>33;37;38;0;0</t>
-  </si>
-  <si>
-    <t>34;2;2;0;0</t>
-  </si>
-  <si>
-    <t>35;39;40;0;0</t>
-  </si>
-  <si>
-    <t>36;41;42;0;0</t>
-  </si>
-  <si>
-    <t>37;15;15;0;0</t>
-  </si>
-  <si>
-    <t>38;43;44;0;0</t>
-  </si>
-  <si>
-    <t>39;45;46;0;0</t>
-  </si>
-  <si>
-    <t>40;47;48;0;0</t>
-  </si>
-  <si>
-    <t>41;49;50;0;0</t>
-  </si>
-  <si>
-    <t>42;2;2;0;0</t>
-  </si>
-  <si>
-    <t>43;16;16;0;0</t>
-  </si>
-  <si>
-    <t>44;17;17;0;0</t>
-  </si>
-  <si>
-    <t>45;51;52;0;0</t>
-  </si>
-  <si>
-    <t>46;3;4;0;0</t>
-  </si>
-  <si>
-    <t>47;104;105;0;0</t>
-  </si>
-  <si>
-    <t>48;5;5;0;0</t>
-  </si>
-  <si>
-    <t>49;12;12;0;0</t>
-  </si>
-  <si>
-    <t>50;106;107;0;0</t>
-  </si>
-  <si>
-    <t>51;108;109;0;0</t>
-  </si>
-  <si>
-    <t>52;6;6;0;0</t>
-  </si>
-  <si>
-    <t>53;0;0;0;0</t>
-  </si>
-  <si>
-    <t>54;53;53;0;0</t>
-  </si>
-  <si>
-    <t>55;53;53;0;0</t>
-  </si>
-  <si>
-    <t>56;54;54;0;0</t>
-  </si>
-  <si>
-    <t>57;54;54;0;0</t>
-  </si>
-  <si>
-    <t>58;56;56;0;0</t>
-  </si>
-  <si>
-    <t>59;56;56;0;0</t>
-  </si>
-  <si>
-    <t>60;58;58;0;0</t>
-  </si>
-  <si>
-    <t>61;58;58;0;0</t>
-  </si>
-  <si>
-    <t>62;60;60;0;0</t>
-  </si>
-  <si>
-    <t>63;60;60;0;0</t>
-  </si>
-  <si>
-    <t>64;62;62;0;0</t>
-  </si>
-  <si>
-    <t>65;62;62;0;0</t>
-  </si>
-  <si>
-    <t>66;64;64;0;0</t>
-  </si>
-  <si>
-    <t>67;65;65;0;0</t>
-  </si>
-  <si>
-    <t>68;65;65;0;0</t>
-  </si>
-  <si>
-    <t>69;66;66;0;0</t>
-  </si>
-  <si>
-    <t>70;66;66;0;0</t>
-  </si>
-  <si>
-    <t>71;68;68;0;0</t>
-  </si>
-  <si>
-    <t>72;68;68;0;0</t>
-  </si>
-  <si>
-    <t>73;69;69;0;0</t>
-  </si>
-  <si>
-    <t>74;69;69;0;0</t>
-  </si>
-  <si>
-    <t>75;71;71;0;0</t>
-  </si>
-  <si>
-    <t>76;71;71;0;0</t>
-  </si>
-  <si>
-    <t>77;73;73;0;0</t>
-  </si>
-  <si>
-    <t>78;73;73;0;0</t>
-  </si>
-  <si>
-    <t>79;0;0;0;0</t>
-  </si>
-  <si>
-    <t>80;79;79;0;0</t>
-  </si>
-  <si>
-    <t>81;79;79;0;0</t>
-  </si>
-  <si>
-    <t>82;80;80;0;0</t>
-  </si>
-  <si>
-    <t>83;80;80;0;0</t>
-  </si>
-  <si>
-    <t>84;81;81;0;0</t>
-  </si>
-  <si>
-    <t>85;81;81;0;0</t>
-  </si>
-  <si>
-    <t>86;83;83;0;0</t>
-  </si>
-  <si>
-    <t>87;83;83;0;0</t>
-  </si>
-  <si>
-    <t>88;84;84;0;0</t>
-  </si>
-  <si>
-    <t>89;84;84;0;0</t>
-  </si>
-  <si>
-    <t>90;86;86;0;0</t>
-  </si>
-  <si>
-    <t>91;87;87;0;0</t>
-  </si>
-  <si>
-    <t>92;88;88;0;0</t>
-  </si>
-  <si>
-    <t>93;89;89;0;0</t>
-  </si>
-  <si>
-    <t>94;90;90;0;0</t>
-  </si>
-  <si>
-    <t>95;90;90;0;0</t>
-  </si>
-  <si>
-    <t>96;92;92;0;0</t>
-  </si>
-  <si>
-    <t>97;92;92;0;0</t>
-  </si>
-  <si>
-    <t>98;26;26;0;0</t>
-  </si>
-  <si>
-    <t>99;27;27;0;0</t>
-  </si>
-  <si>
-    <t>100;1;1;0;0</t>
-  </si>
-  <si>
-    <t>101;1;1;0;0</t>
-  </si>
-  <si>
-    <t>102;1;1;0;0</t>
-  </si>
-  <si>
-    <t>103;1;1;0;0</t>
-  </si>
-  <si>
-    <t>104;7;7;0;0</t>
-  </si>
-  <si>
-    <t>105;10;10;0;0</t>
-  </si>
-  <si>
-    <t>106;13;13;0;0</t>
-  </si>
-  <si>
-    <t>107;14;14;0;0</t>
-  </si>
-  <si>
-    <t>108;110;111;0;0</t>
-  </si>
-  <si>
-    <t>109;9;9;0;0</t>
-  </si>
-  <si>
-    <t>110;112;113;0;0</t>
-  </si>
-  <si>
-    <t>111;8;8;0;0</t>
-  </si>
-  <si>
-    <t>112;114;115;0;0</t>
-  </si>
-  <si>
-    <t>113;116;117;0;0</t>
-  </si>
-  <si>
-    <t>114;18;18;0;0</t>
-  </si>
-  <si>
-    <t>115;118;119;0;0</t>
-  </si>
-  <si>
-    <t>116;22;22;0;0</t>
-  </si>
-  <si>
-    <t>117;120;121;0;0</t>
-  </si>
-  <si>
-    <t>118;122;123;0;0</t>
-  </si>
-  <si>
-    <t>119;19;19;0;0</t>
-  </si>
-  <si>
-    <t>120;124;125;0;0</t>
-  </si>
-  <si>
-    <t>121;23;23;0;0</t>
-  </si>
-  <si>
-    <t>122;21;21;0;0</t>
-  </si>
-  <si>
-    <t>123;20;20;0;0</t>
-  </si>
-  <si>
-    <t>124;25;25;0;0</t>
-  </si>
-  <si>
-    <t>125;24;24;0;0</t>
-  </si>
-  <si>
-    <t>126;98;99;0;0</t>
-  </si>
-  <si>
-    <t>0;126;126;0;0.955</t>
+    <t>LocationIDNumber;OutFlowA;OutFlowB;OutFlowC;DwellTime(s);SplittingRatioKey</t>
+  </si>
+  <si>
+    <t>28;29;30;0;0;B</t>
+  </si>
+  <si>
+    <t>0;126;126;0;0.955;0</t>
+  </si>
+  <si>
+    <t>1;28;28;0;1;0</t>
+  </si>
+  <si>
+    <t>3;11;11;0;37.90;0</t>
+  </si>
+  <si>
+    <t>4;11;11;0;29.35;0</t>
+  </si>
+  <si>
+    <t>5;11;11;0;68.23;0</t>
+  </si>
+  <si>
+    <t>6;63;63;0;5.15;0</t>
+  </si>
+  <si>
+    <t>7;11;11;0;42.14;0</t>
+  </si>
+  <si>
+    <t>29;31;32;0;0;C</t>
+  </si>
+  <si>
+    <t>8;11;11;0;46.22;0</t>
+  </si>
+  <si>
+    <t>9;61;61;0;5.15;0</t>
+  </si>
+  <si>
+    <t>12;96;96;0;17.89;0</t>
+  </si>
+  <si>
+    <t>13;97;97;0;17.89;0</t>
+  </si>
+  <si>
+    <t>14;93;93;0;17.89;0</t>
+  </si>
+  <si>
+    <t>15;94;94;0;17.89;0</t>
+  </si>
+  <si>
+    <t>16;95;95;0;17.89;0</t>
+  </si>
+  <si>
+    <t>17;91;91;0;17.89;0</t>
+  </si>
+  <si>
+    <t>18;67;67;0;39.92;0</t>
+  </si>
+  <si>
+    <t>19;72;72;0;39.92;0</t>
+  </si>
+  <si>
+    <t>20;76;76;0;39.92;0</t>
+  </si>
+  <si>
+    <t>21;75;75;0;39.92;0</t>
+  </si>
+  <si>
+    <t>22;70;70;0;39.92;0</t>
+  </si>
+  <si>
+    <t>23;74;74;0;39.92;0</t>
+  </si>
+  <si>
+    <t>24;78;78;0;39.92;0</t>
+  </si>
+  <si>
+    <t>30;33;34;0;0;D</t>
+  </si>
+  <si>
+    <t>25;77;77;0;39.92;0</t>
+  </si>
+  <si>
+    <t>31;35;36;0;0;E</t>
+  </si>
+  <si>
+    <t>32;2;2;0;0;0</t>
+  </si>
+  <si>
+    <t>33;37;38;0;0;F</t>
+  </si>
+  <si>
+    <t>34;2;2;0;0;0</t>
+  </si>
+  <si>
+    <t>35;39;40;0;0;G</t>
+  </si>
+  <si>
+    <t>36;41;42;0;0;H</t>
+  </si>
+  <si>
+    <t>37;15;15;0;0;0</t>
+  </si>
+  <si>
+    <t>38;43;44;0;0;I</t>
+  </si>
+  <si>
+    <t>39;45;46;0;0;J</t>
+  </si>
+  <si>
+    <t>40;47;48;0;0;K</t>
+  </si>
+  <si>
+    <t>41;49;50;0;0;L</t>
+  </si>
+  <si>
+    <t>42;2;2;0;0;0</t>
+  </si>
+  <si>
+    <t>43;16;16;0;0;0</t>
+  </si>
+  <si>
+    <t>44;17;17;0;0;0</t>
+  </si>
+  <si>
+    <t>45;51;52;0;0;M</t>
+  </si>
+  <si>
+    <t>46;3;4;0;0;N</t>
+  </si>
+  <si>
+    <t>47;104;105;0;0;O</t>
+  </si>
+  <si>
+    <t>48;5;5;0;0;0</t>
+  </si>
+  <si>
+    <t>49;12;12;0;0;0</t>
+  </si>
+  <si>
+    <t>50;106;107;0;0;P</t>
+  </si>
+  <si>
+    <t>51;108;109;0;0;Q</t>
+  </si>
+  <si>
+    <t>52;6;6;0;0;0</t>
+  </si>
+  <si>
+    <t>53;0;0;0;0;0</t>
+  </si>
+  <si>
+    <t>54;53;53;0;0;0</t>
+  </si>
+  <si>
+    <t>55;53;53;0;0;0</t>
+  </si>
+  <si>
+    <t>56;54;54;0;0;0</t>
+  </si>
+  <si>
+    <t>57;54;54;0;0;0</t>
+  </si>
+  <si>
+    <t>58;56;56;0;0;0</t>
+  </si>
+  <si>
+    <t>59;56;56;0;0;0</t>
+  </si>
+  <si>
+    <t>60;58;58;0;0;0</t>
+  </si>
+  <si>
+    <t>61;58;58;0;0;0</t>
+  </si>
+  <si>
+    <t>62;60;60;0;0;0</t>
+  </si>
+  <si>
+    <t>63;60;60;0;0;0</t>
+  </si>
+  <si>
+    <t>64;62;62;0;0;0</t>
+  </si>
+  <si>
+    <t>65;62;62;0;0;0</t>
+  </si>
+  <si>
+    <t>66;64;64;0;0;0</t>
+  </si>
+  <si>
+    <t>67;65;65;0;0;0</t>
+  </si>
+  <si>
+    <t>68;65;65;0;0;0</t>
+  </si>
+  <si>
+    <t>69;66;66;0;0;0</t>
+  </si>
+  <si>
+    <t>70;66;66;0;0;0</t>
+  </si>
+  <si>
+    <t>71;68;68;0;0;0</t>
+  </si>
+  <si>
+    <t>72;68;68;0;0;0</t>
+  </si>
+  <si>
+    <t>73;69;69;0;0;0</t>
+  </si>
+  <si>
+    <t>74;69;69;0;0;0</t>
+  </si>
+  <si>
+    <t>75;71;71;0;0;0</t>
+  </si>
+  <si>
+    <t>76;71;71;0;0;0</t>
+  </si>
+  <si>
+    <t>77;73;73;0;0;0</t>
+  </si>
+  <si>
+    <t>78;73;73;0;0;0</t>
+  </si>
+  <si>
+    <t>79;0;0;0;0;0</t>
+  </si>
+  <si>
+    <t>80;79;79;0;0;0</t>
+  </si>
+  <si>
+    <t>81;79;79;0;0;0</t>
+  </si>
+  <si>
+    <t>82;80;80;0;0;0</t>
+  </si>
+  <si>
+    <t>83;80;80;0;0;0</t>
+  </si>
+  <si>
+    <t>84;81;81;0;0;0</t>
+  </si>
+  <si>
+    <t>85;81;81;0;0;0</t>
+  </si>
+  <si>
+    <t>86;83;83;0;0;0</t>
+  </si>
+  <si>
+    <t>87;83;83;0;0;0</t>
+  </si>
+  <si>
+    <t>88;84;84;0;0;0</t>
+  </si>
+  <si>
+    <t>89;84;84;0;0;0</t>
+  </si>
+  <si>
+    <t>90;86;86;0;0;0</t>
+  </si>
+  <si>
+    <t>91;87;87;0;0;0</t>
+  </si>
+  <si>
+    <t>92;88;88;0;0;0</t>
+  </si>
+  <si>
+    <t>93;89;89;0;0;0</t>
+  </si>
+  <si>
+    <t>94;90;90;0;0;0</t>
+  </si>
+  <si>
+    <t>95;90;90;0;0;0</t>
+  </si>
+  <si>
+    <t>96;92;92;0;0;0</t>
+  </si>
+  <si>
+    <t>97;92;92;0;0;0</t>
+  </si>
+  <si>
+    <t>98;26;26;0;0;0</t>
+  </si>
+  <si>
+    <t>99;27;27;0;0;0</t>
+  </si>
+  <si>
+    <t>100;1;1;0;0;0</t>
+  </si>
+  <si>
+    <t>101;1;1;0;0;0</t>
+  </si>
+  <si>
+    <t>102;1;1;0;0;0</t>
+  </si>
+  <si>
+    <t>103;1;1;0;0;0</t>
+  </si>
+  <si>
+    <t>104;7;7;0;0;0</t>
+  </si>
+  <si>
+    <t>105;10;10;0;0;0</t>
+  </si>
+  <si>
+    <t>106;13;13;0;0;0</t>
+  </si>
+  <si>
+    <t>107;14;14;0;0;0</t>
+  </si>
+  <si>
+    <t>108;110;111;0;0;R</t>
+  </si>
+  <si>
+    <t>109;9;9;0;0;0</t>
+  </si>
+  <si>
+    <t>110;112;113;0;0;S</t>
+  </si>
+  <si>
+    <t>111;8;8;0;0;0</t>
+  </si>
+  <si>
+    <t>112;114;115;0;0;T</t>
+  </si>
+  <si>
+    <t>113;116;117;0;0;U</t>
+  </si>
+  <si>
+    <t>114;18;18;0;0;0</t>
+  </si>
+  <si>
+    <t>115;118;119;0;0;V</t>
+  </si>
+  <si>
+    <t>116;22;22;0;0;0</t>
+  </si>
+  <si>
+    <t>117;120;121;0;0;W</t>
+  </si>
+  <si>
+    <t>118;122;123;0;0;X</t>
+  </si>
+  <si>
+    <t>119;19;19;0;0;0</t>
+  </si>
+  <si>
+    <t>120;124;125;0;0;Y</t>
+  </si>
+  <si>
+    <t>121;23;23;0;0;0</t>
+  </si>
+  <si>
+    <t>122;21;21;0;0;0</t>
+  </si>
+  <si>
+    <t>123;20;20;0;0;0</t>
+  </si>
+  <si>
+    <t>124;25;25;0;0;0</t>
+  </si>
+  <si>
+    <t>125;24;24;0;0;0</t>
+  </si>
+  <si>
+    <t>2;82;85;0;4.89;Z</t>
+  </si>
+  <si>
+    <t>10;55;57;59;18.82;AA</t>
+  </si>
+  <si>
+    <t>11;55;57;59;19.31;AA</t>
+  </si>
+  <si>
+    <t>26;100;103;0;5.14;AB</t>
+  </si>
+  <si>
+    <t>27;101;102;0;5.14;AC</t>
+  </si>
+  <si>
+    <t>126;98;99;0;0;AD</t>
   </si>
 </sst>
 </file>
@@ -3994,13 +3995,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09A48F57-DE8B-4C09-80D7-46260E48A147}">
   <dimension ref="A1:B128"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.06640625" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>932</v>
       </c>
@@ -4008,103 +4009,103 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>936</v>
       </c>
       <c r="B2" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>935</v>
       </c>
       <c r="B3" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>817</v>
       </c>
       <c r="B4" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>844</v>
       </c>
       <c r="B5" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>845</v>
       </c>
       <c r="B6" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>818</v>
       </c>
       <c r="B7" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>807</v>
       </c>
       <c r="B8" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>819</v>
       </c>
       <c r="B9" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>846</v>
       </c>
       <c r="B10" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>811</v>
       </c>
       <c r="B11" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>848</v>
       </c>
       <c r="B12" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>847</v>
       </c>
       <c r="B13" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1007</v>
       </c>
@@ -4112,7 +4113,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1008</v>
       </c>
@@ -4120,7 +4121,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1009</v>
       </c>
@@ -4128,7 +4129,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1010</v>
       </c>
@@ -4136,7 +4137,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1022</v>
       </c>
@@ -4144,7 +4145,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1011</v>
       </c>
@@ -4152,7 +4153,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1014</v>
       </c>
@@ -4160,7 +4161,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>1015</v>
       </c>
@@ -4168,7 +4169,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1016</v>
       </c>
@@ -4176,7 +4177,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1017</v>
       </c>
@@ -4184,7 +4185,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1018</v>
       </c>
@@ -4192,7 +4193,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1019</v>
       </c>
@@ -4200,7 +4201,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1020</v>
       </c>
@@ -4208,820 +4209,820 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>1021</v>
       </c>
       <c r="B27" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>1012</v>
       </c>
       <c r="B28" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>1013</v>
       </c>
       <c r="B29" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>963</v>
       </c>
       <c r="B30" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>964</v>
       </c>
       <c r="B31" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>965</v>
       </c>
       <c r="B32" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>966</v>
       </c>
       <c r="B33" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>967</v>
       </c>
       <c r="B34" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>968</v>
       </c>
       <c r="B35" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>969</v>
       </c>
       <c r="B36" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>970</v>
       </c>
       <c r="B37" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>971</v>
       </c>
       <c r="B38" t="s">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>972</v>
       </c>
       <c r="B39" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>973</v>
       </c>
       <c r="B40" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>974</v>
       </c>
       <c r="B41" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>975</v>
       </c>
       <c r="B42" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>976</v>
       </c>
       <c r="B43" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>977</v>
       </c>
       <c r="B44" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>978</v>
       </c>
       <c r="B45" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>979</v>
       </c>
       <c r="B46" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>980</v>
       </c>
       <c r="B47" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>981</v>
       </c>
       <c r="B48" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>982</v>
       </c>
       <c r="B49" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>983</v>
       </c>
       <c r="B50" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>984</v>
       </c>
       <c r="B51" t="s">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>985</v>
       </c>
       <c r="B52" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>986</v>
       </c>
       <c r="B53" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>987</v>
       </c>
       <c r="B54" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>937</v>
       </c>
       <c r="B55" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>938</v>
       </c>
       <c r="B56" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>939</v>
       </c>
       <c r="B57" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>940</v>
       </c>
       <c r="B58" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>941</v>
       </c>
       <c r="B59" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>942</v>
       </c>
       <c r="B60" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>943</v>
       </c>
       <c r="B61" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>944</v>
       </c>
       <c r="B62" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>945</v>
       </c>
       <c r="B63" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>946</v>
       </c>
       <c r="B64" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>947</v>
       </c>
       <c r="B65" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>948</v>
       </c>
       <c r="B66" t="s">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>949</v>
       </c>
       <c r="B67" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>950</v>
       </c>
       <c r="B68" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>951</v>
       </c>
       <c r="B69" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>952</v>
       </c>
       <c r="B70" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>953</v>
       </c>
       <c r="B71" t="s">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>954</v>
       </c>
       <c r="B72" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>955</v>
       </c>
       <c r="B73" t="s">
-        <v>1116</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>956</v>
       </c>
       <c r="B74" t="s">
-        <v>1117</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>957</v>
       </c>
       <c r="B75" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>958</v>
       </c>
       <c r="B76" t="s">
-        <v>1119</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>959</v>
       </c>
       <c r="B77" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>960</v>
       </c>
       <c r="B78" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>961</v>
       </c>
       <c r="B79" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>962</v>
       </c>
       <c r="B80" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>988</v>
       </c>
       <c r="B81" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>989</v>
       </c>
       <c r="B82" t="s">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>990</v>
       </c>
       <c r="B83" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>991</v>
       </c>
       <c r="B84" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>992</v>
       </c>
       <c r="B85" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>993</v>
       </c>
       <c r="B86" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>994</v>
       </c>
       <c r="B87" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>995</v>
       </c>
       <c r="B88" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>996</v>
       </c>
       <c r="B89" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>997</v>
       </c>
       <c r="B90" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>998</v>
       </c>
       <c r="B91" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>999</v>
       </c>
       <c r="B92" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>1000</v>
       </c>
       <c r="B93" t="s">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>1001</v>
       </c>
       <c r="B94" t="s">
-        <v>1137</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>1002</v>
       </c>
       <c r="B95" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>1003</v>
       </c>
       <c r="B96" t="s">
-        <v>1139</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>1004</v>
       </c>
       <c r="B97" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>1005</v>
       </c>
       <c r="B98" t="s">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>1006</v>
       </c>
       <c r="B99" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>140</v>
       </c>
       <c r="B100" t="s">
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>927</v>
       </c>
       <c r="B101" t="s">
-        <v>1144</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>928</v>
       </c>
       <c r="B102" t="s">
-        <v>1145</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>929</v>
       </c>
       <c r="B103" t="s">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>930</v>
       </c>
       <c r="B104" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>931</v>
       </c>
       <c r="B105" t="s">
-        <v>1148</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>1023</v>
       </c>
       <c r="B106" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>1024</v>
       </c>
       <c r="B107" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>1025</v>
       </c>
       <c r="B108" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>1026</v>
       </c>
       <c r="B109" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>1027</v>
       </c>
       <c r="B110" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>1028</v>
       </c>
       <c r="B111" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1029</v>
       </c>
       <c r="B112" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>1030</v>
       </c>
       <c r="B113" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>1031</v>
       </c>
       <c r="B114" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>1032</v>
       </c>
       <c r="B115" t="s">
-        <v>1158</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>1033</v>
       </c>
       <c r="B116" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>1034</v>
       </c>
       <c r="B117" t="s">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>1035</v>
       </c>
       <c r="B118" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>1036</v>
       </c>
       <c r="B119" t="s">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>1037</v>
       </c>
       <c r="B120" t="s">
-        <v>1163</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>1038</v>
       </c>
       <c r="B121" t="s">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>1039</v>
       </c>
       <c r="B122" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>1040</v>
       </c>
       <c r="B123" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>1041</v>
       </c>
       <c r="B124" t="s">
-        <v>1167</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>1042</v>
       </c>
       <c r="B125" t="s">
-        <v>1168</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>1043</v>
       </c>
       <c r="B126" t="s">
-        <v>1169</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>1044</v>
       </c>
       <c r="B127" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
   </sheetData>
@@ -5032,19 +5033,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G179"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.265625" customWidth="1"/>
-    <col min="2" max="2" width="30.73046875" customWidth="1"/>
-    <col min="3" max="3" width="56.3984375" customWidth="1"/>
-    <col min="4" max="4" width="67.59765625" customWidth="1"/>
-    <col min="5" max="5" width="26.3984375" customWidth="1"/>
-    <col min="6" max="6" width="7.86328125" customWidth="1"/>
-    <col min="7" max="7" width="25.3984375" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="56.42578125" customWidth="1"/>
+    <col min="4" max="4" width="67.5703125" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" customWidth="1"/>
+    <col min="7" max="7" width="25.42578125" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5064,7 +5065,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -5084,7 +5085,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -5101,7 +5102,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -5115,7 +5116,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -5129,7 +5130,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -5143,7 +5144,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -5160,7 +5161,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -5180,7 +5181,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -5194,7 +5195,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -5211,7 +5212,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -5225,7 +5226,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -5245,7 +5246,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -5259,7 +5260,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -5279,7 +5280,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>774</v>
       </c>
@@ -5290,7 +5291,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -5304,7 +5305,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -5318,7 +5319,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -5332,7 +5333,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -5346,7 +5347,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -5360,7 +5361,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -5377,7 +5378,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -5394,7 +5395,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -5408,7 +5409,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -5422,7 +5423,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -5436,7 +5437,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>35</v>
       </c>
@@ -5450,7 +5451,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>36</v>
       </c>
@@ -5464,7 +5465,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -5481,7 +5482,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -5495,7 +5496,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -5512,7 +5513,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -5529,7 +5530,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>41</v>
       </c>
@@ -5546,7 +5547,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -5560,7 +5561,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>43</v>
       </c>
@@ -5577,7 +5578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>44</v>
       </c>
@@ -5594,7 +5595,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>45</v>
       </c>
@@ -5608,7 +5609,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -5622,7 +5623,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>47</v>
       </c>
@@ -5639,7 +5640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>48</v>
       </c>
@@ -5656,7 +5657,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>49</v>
       </c>
@@ -5670,7 +5671,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -5687,7 +5688,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>51</v>
       </c>
@@ -5701,7 +5702,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>52</v>
       </c>
@@ -5718,7 +5719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>53</v>
       </c>
@@ -5732,7 +5733,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>54</v>
       </c>
@@ -5749,7 +5750,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>55</v>
       </c>
@@ -5763,7 +5764,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>56</v>
       </c>
@@ -5777,7 +5778,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>57</v>
       </c>
@@ -5797,7 +5798,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>58</v>
       </c>
@@ -5811,7 +5812,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>59</v>
       </c>
@@ -5825,7 +5826,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>60</v>
       </c>
@@ -5839,7 +5840,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>61</v>
       </c>
@@ -5853,7 +5854,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>62</v>
       </c>
@@ -5867,7 +5868,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -5881,7 +5882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>84</v>
       </c>
@@ -5898,7 +5899,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>85</v>
       </c>
@@ -5915,7 +5916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>86</v>
       </c>
@@ -5929,7 +5930,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>87</v>
       </c>
@@ -5943,7 +5944,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>88</v>
       </c>
@@ -5960,7 +5961,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>89</v>
       </c>
@@ -5974,7 +5975,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>90</v>
       </c>
@@ -5988,7 +5989,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>91</v>
       </c>
@@ -6002,7 +6003,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>92</v>
       </c>
@@ -6019,7 +6020,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>93</v>
       </c>
@@ -6033,7 +6034,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>94</v>
       </c>
@@ -6047,7 +6048,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>95</v>
       </c>
@@ -6064,7 +6065,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>100</v>
       </c>
@@ -6078,7 +6079,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>101</v>
       </c>
@@ -6092,7 +6093,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>102</v>
       </c>
@@ -6106,7 +6107,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>103</v>
       </c>
@@ -6120,7 +6121,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>104</v>
       </c>
@@ -6134,7 +6135,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>105</v>
       </c>
@@ -6151,7 +6152,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>106</v>
       </c>
@@ -6168,7 +6169,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>107</v>
       </c>
@@ -6182,7 +6183,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>108</v>
       </c>
@@ -6196,7 +6197,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>109</v>
       </c>
@@ -6213,7 +6214,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>110</v>
       </c>
@@ -6230,7 +6231,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>111</v>
       </c>
@@ -6244,7 +6245,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>112</v>
       </c>
@@ -6258,7 +6259,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>113</v>
       </c>
@@ -6272,7 +6273,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>114</v>
       </c>
@@ -6286,7 +6287,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>115</v>
       </c>
@@ -6303,7 +6304,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>116</v>
       </c>
@@ -6317,7 +6318,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>117</v>
       </c>
@@ -6334,7 +6335,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>118</v>
       </c>
@@ -6351,7 +6352,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>119</v>
       </c>
@@ -6368,7 +6369,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>120</v>
       </c>
@@ -6382,7 +6383,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>121</v>
       </c>
@@ -6396,7 +6397,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>122</v>
       </c>
@@ -6410,7 +6411,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>123</v>
       </c>
@@ -6424,7 +6425,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>124</v>
       </c>
@@ -6438,7 +6439,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>125</v>
       </c>
@@ -6455,7 +6456,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>126</v>
       </c>
@@ -6472,7 +6473,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>131</v>
       </c>
@@ -6486,7 +6487,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>132</v>
       </c>
@@ -6500,7 +6501,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>133</v>
       </c>
@@ -6514,7 +6515,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>134</v>
       </c>
@@ -6528,7 +6529,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>135</v>
       </c>
@@ -6542,7 +6543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>136</v>
       </c>
@@ -6556,7 +6557,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>137</v>
       </c>
@@ -6570,7 +6571,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>367</v>
       </c>
@@ -6587,7 +6588,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>368</v>
       </c>
@@ -6601,7 +6602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>369</v>
       </c>
@@ -6618,7 +6619,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>370</v>
       </c>
@@ -6632,7 +6633,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>371</v>
       </c>
@@ -6649,7 +6650,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>372</v>
       </c>
@@ -6666,7 +6667,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>373</v>
       </c>
@@ -6680,7 +6681,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>374</v>
       </c>
@@ -6694,7 +6695,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>375</v>
       </c>
@@ -6708,7 +6709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>376</v>
       </c>
@@ -6722,7 +6723,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>377</v>
       </c>
@@ -6736,7 +6737,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>378</v>
       </c>
@@ -6750,7 +6751,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>379</v>
       </c>
@@ -6764,7 +6765,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>380</v>
       </c>
@@ -6778,7 +6779,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>381</v>
       </c>
@@ -6792,7 +6793,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>382</v>
       </c>
@@ -6806,7 +6807,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>383</v>
       </c>
@@ -6820,7 +6821,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>384</v>
       </c>
@@ -6834,7 +6835,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>385</v>
       </c>
@@ -6851,7 +6852,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>386</v>
       </c>
@@ -6868,7 +6869,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>387</v>
       </c>
@@ -6882,7 +6883,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>619</v>
       </c>
@@ -6899,7 +6900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>620</v>
       </c>
@@ -6913,7 +6914,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>621</v>
       </c>
@@ -6930,7 +6931,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>622</v>
       </c>
@@ -6944,7 +6945,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>623</v>
       </c>
@@ -6958,7 +6959,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>624</v>
       </c>
@@ -6975,7 +6976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>625</v>
       </c>
@@ -6992,7 +6993,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>626</v>
       </c>
@@ -7006,7 +7007,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>627</v>
       </c>
@@ -7020,7 +7021,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>628</v>
       </c>
@@ -7037,7 +7038,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>629</v>
       </c>
@@ -7051,7 +7052,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>630</v>
       </c>
@@ -7065,7 +7066,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>631</v>
       </c>
@@ -7079,7 +7080,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>632</v>
       </c>
@@ -7096,7 +7097,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>633</v>
       </c>
@@ -7110,7 +7111,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>634</v>
       </c>
@@ -7124,7 +7125,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>635</v>
       </c>
@@ -7138,7 +7139,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>636</v>
       </c>
@@ -7152,7 +7153,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>644</v>
       </c>
@@ -7169,7 +7170,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>645</v>
       </c>
@@ -7183,7 +7184,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>646</v>
       </c>
@@ -7200,7 +7201,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>647</v>
       </c>
@@ -7217,7 +7218,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>648</v>
       </c>
@@ -7231,7 +7232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>649</v>
       </c>
@@ -7248,7 +7249,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>650</v>
       </c>
@@ -7262,7 +7263,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>651</v>
       </c>
@@ -7276,7 +7277,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>652</v>
       </c>
@@ -7290,7 +7291,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>653</v>
       </c>
@@ -7307,7 +7308,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>654</v>
       </c>
@@ -7321,7 +7322,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>655</v>
       </c>
@@ -7335,7 +7336,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>656</v>
       </c>
@@ -7349,7 +7350,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>660</v>
       </c>
@@ -7363,7 +7364,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>661</v>
       </c>
@@ -7380,7 +7381,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>662</v>
       </c>
@@ -7394,7 +7395,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>663</v>
       </c>
@@ -7408,7 +7409,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>664</v>
       </c>
@@ -7422,7 +7423,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>665</v>
       </c>
@@ -7439,7 +7440,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>666</v>
       </c>
@@ -7453,7 +7454,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>667</v>
       </c>
@@ -7470,7 +7471,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>668</v>
       </c>
@@ -7487,7 +7488,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>669</v>
       </c>
@@ -7501,7 +7502,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>670</v>
       </c>
@@ -7518,7 +7519,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>671</v>
       </c>
@@ -7532,7 +7533,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>672</v>
       </c>
@@ -7546,7 +7547,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>673</v>
       </c>
@@ -7563,7 +7564,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>674</v>
       </c>
@@ -7580,7 +7581,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>675</v>
       </c>
@@ -7597,7 +7598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>676</v>
       </c>
@@ -7611,7 +7612,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>677</v>
       </c>
@@ -7625,7 +7626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>678</v>
       </c>
@@ -7639,7 +7640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>679</v>
       </c>
@@ -7656,7 +7657,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>680</v>
       </c>
@@ -7670,7 +7671,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>681</v>
       </c>
@@ -7684,7 +7685,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>682</v>
       </c>
@@ -7698,7 +7699,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>683</v>
       </c>
@@ -7712,7 +7713,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>684</v>
       </c>
@@ -7726,7 +7727,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>685</v>
       </c>
@@ -7743,7 +7744,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>686</v>
       </c>
@@ -7775,16 +7776,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.3984375" customWidth="1"/>
-    <col min="2" max="2" width="28.1328125" customWidth="1"/>
-    <col min="3" max="3" width="13.3984375" customWidth="1"/>
-    <col min="4" max="5" width="39.86328125" customWidth="1"/>
-    <col min="6" max="6" width="18.1328125" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="5" width="39.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7810,7 +7811,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -7824,7 +7825,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>694</v>
       </c>
@@ -7832,7 +7833,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>695</v>
       </c>
@@ -7846,7 +7847,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>696</v>
       </c>
@@ -7860,7 +7861,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>697</v>
       </c>
@@ -7874,7 +7875,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>698</v>
       </c>
@@ -7888,7 +7889,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>793</v>
       </c>
@@ -7902,7 +7903,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>794</v>
       </c>
@@ -7916,7 +7917,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>781</v>
       </c>
@@ -7927,7 +7928,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>795</v>
       </c>
@@ -7935,7 +7936,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>796</v>
       </c>
@@ -7943,7 +7944,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>782</v>
       </c>
@@ -7954,7 +7955,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>797</v>
       </c>
@@ -7962,7 +7963,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>798</v>
       </c>
@@ -7979,18 +7980,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E258076-C214-41D6-BCD6-F667F1858984}">
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="28.1328125" customWidth="1"/>
-    <col min="3" max="3" width="14.59765625" customWidth="1"/>
-    <col min="4" max="4" width="119.59765625" customWidth="1"/>
-    <col min="5" max="5" width="18.59765625" customWidth="1"/>
-    <col min="6" max="6" width="18.1328125" customWidth="1"/>
-    <col min="7" max="7" width="13.59765625" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="119.5703125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8016,7 +8017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>775</v>
       </c>
@@ -8033,7 +8034,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>783</v>
       </c>
@@ -8041,7 +8042,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>784</v>
       </c>
@@ -8049,7 +8050,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>785</v>
       </c>
@@ -8057,7 +8058,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>786</v>
       </c>
@@ -8065,7 +8066,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>787</v>
       </c>
@@ -8073,7 +8074,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>699</v>
       </c>
@@ -8084,7 +8085,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>788</v>
       </c>
@@ -8095,7 +8096,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>838</v>
       </c>
@@ -8103,7 +8104,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>789</v>
       </c>
@@ -8111,12 +8112,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>791</v>
       </c>
@@ -8124,12 +8125,12 @@
         <v>896</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>898</v>
       </c>
@@ -8142,19 +8143,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{188388E5-F9D8-4148-BF34-9C51095EB628}">
   <dimension ref="A1:I46"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.265625" customWidth="1"/>
-    <col min="2" max="3" width="12.1328125" customWidth="1"/>
-    <col min="4" max="4" width="24.86328125" customWidth="1"/>
-    <col min="5" max="5" width="25.3984375" customWidth="1"/>
-    <col min="6" max="6" width="36.73046875" customWidth="1"/>
-    <col min="7" max="7" width="26.59765625" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" customWidth="1"/>
+    <col min="2" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" customWidth="1"/>
+    <col min="6" max="6" width="36.7109375" customWidth="1"/>
+    <col min="7" max="7" width="26.5703125" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>858</v>
       </c>
@@ -8177,7 +8178,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -8197,7 +8198,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>79</v>
       </c>
@@ -8217,7 +8218,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>859</v>
       </c>
@@ -8235,7 +8236,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>763</v>
       </c>
@@ -8255,7 +8256,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>860</v>
       </c>
@@ -8273,7 +8274,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>861</v>
       </c>
@@ -8291,7 +8292,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>806</v>
       </c>
@@ -8311,7 +8312,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>808</v>
       </c>
@@ -8331,7 +8332,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>862</v>
       </c>
@@ -8349,7 +8350,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>807</v>
       </c>
@@ -8369,7 +8370,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>809</v>
       </c>
@@ -8389,7 +8390,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>810</v>
       </c>
@@ -8409,7 +8410,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>863</v>
       </c>
@@ -8427,7 +8428,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>864</v>
       </c>
@@ -8445,7 +8446,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>811</v>
       </c>
@@ -8465,7 +8466,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>812</v>
       </c>
@@ -8485,7 +8486,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>813</v>
       </c>
@@ -8503,7 +8504,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>814</v>
       </c>
@@ -8521,7 +8522,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>865</v>
       </c>
@@ -8539,7 +8540,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>866</v>
       </c>
@@ -8557,7 +8558,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>867</v>
       </c>
@@ -8575,7 +8576,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>868</v>
       </c>
@@ -8593,7 +8594,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>869</v>
       </c>
@@ -8611,7 +8612,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>870</v>
       </c>
@@ -8629,7 +8630,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>871</v>
       </c>
@@ -8643,7 +8644,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>872</v>
       </c>
@@ -8657,7 +8658,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>861</v>
       </c>
@@ -8668,7 +8669,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>877</v>
       </c>
@@ -8679,7 +8680,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>873</v>
       </c>
@@ -8690,7 +8691,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>874</v>
       </c>
@@ -8701,7 +8702,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>875</v>
       </c>
@@ -8712,7 +8713,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>876</v>
       </c>
@@ -8723,7 +8724,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>820</v>
       </c>
@@ -8737,7 +8738,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>820</v>
       </c>
@@ -8751,7 +8752,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>820</v>
       </c>
@@ -8765,7 +8766,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>811</v>
       </c>
@@ -8779,7 +8780,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>807</v>
       </c>
@@ -8793,7 +8794,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>813</v>
       </c>
@@ -8804,7 +8805,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>814</v>
       </c>
@@ -8815,7 +8816,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>903</v>
       </c>
@@ -8826,7 +8827,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>866</v>
       </c>
@@ -8837,7 +8838,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>878</v>
       </c>
@@ -8848,7 +8849,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>868</v>
       </c>
@@ -8859,7 +8860,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>879</v>
       </c>
@@ -8870,7 +8871,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>880</v>
       </c>
@@ -8890,20 +8891,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F665A280-B941-4509-8B0A-1E2E1E43C816}">
   <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.265625" customWidth="1"/>
-    <col min="2" max="2" width="20.3984375" customWidth="1"/>
-    <col min="3" max="3" width="21.265625" customWidth="1"/>
-    <col min="4" max="4" width="30.1328125" customWidth="1"/>
-    <col min="5" max="7" width="18.73046875" customWidth="1"/>
-    <col min="8" max="8" width="15.3984375" customWidth="1"/>
-    <col min="9" max="9" width="23.86328125" customWidth="1"/>
-    <col min="10" max="10" width="13.265625" customWidth="1"/>
-    <col min="11" max="11" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="39.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" customWidth="1"/>
+    <col min="4" max="4" width="30.140625" customWidth="1"/>
+    <col min="5" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" customWidth="1"/>
+    <col min="9" max="9" width="23.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>843</v>
       </c>
@@ -8935,7 +8936,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>817</v>
       </c>
@@ -8965,7 +8966,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>844</v>
       </c>
@@ -8986,7 +8987,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>845</v>
       </c>
@@ -9013,7 +9014,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>818</v>
       </c>
@@ -9042,7 +9043,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>807</v>
       </c>
@@ -9072,7 +9073,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>819</v>
       </c>
@@ -9099,7 +9100,7 @@
         <v>27.213699999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>846</v>
       </c>
@@ -9120,7 +9121,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>811</v>
       </c>
@@ -9141,7 +9142,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>848</v>
       </c>
@@ -9166,7 +9167,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>847</v>
       </c>
@@ -9190,7 +9191,7 @@
       <c r="G11" s="6"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>913</v>
       </c>
@@ -9217,7 +9218,7 @@
         <v>0.12507649418644184</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>914</v>
       </c>
@@ -9244,7 +9245,7 @@
         <v>0.11842999932005169</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>915</v>
       </c>
@@ -9273,7 +9274,7 @@
         <v>5.0758142381179039E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>916</v>
       </c>
@@ -9302,7 +9303,7 @@
         <v>0.17563212646571397</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>917</v>
       </c>
@@ -9331,7 +9332,7 @@
         <v>0.38873802533282864</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>918</v>
       </c>
@@ -9360,7 +9361,7 @@
         <v>4.7457714313011469E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>919</v>
       </c>
@@ -9389,7 +9390,7 @@
         <v>5.1400581324847414E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>934</v>
       </c>
@@ -9408,7 +9409,7 @@
         <v>5.1369230769230771</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>933</v>
       </c>
@@ -9436,16 +9437,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A49E26-2F33-4C48-B568-5BD877D54B87}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="18.1328125" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18.86328125" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9462,32 +9463,32 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>931</v>
       </c>
@@ -9500,16 +9501,16 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83BDF3EF-B0DD-4EA1-9C5E-4B5CEDCAFD48}">
   <dimension ref="A1:G400"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.265625" customWidth="1"/>
-    <col min="2" max="2" width="33.73046875" customWidth="1"/>
-    <col min="3" max="3" width="49.73046875" customWidth="1"/>
-    <col min="4" max="4" width="67.265625" customWidth="1"/>
-    <col min="5" max="5" width="53.265625" customWidth="1"/>
+    <col min="1" max="1" width="27.28515625" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" customWidth="1"/>
+    <col min="3" max="3" width="49.7109375" customWidth="1"/>
+    <col min="4" max="4" width="67.28515625" customWidth="1"/>
+    <col min="5" max="5" width="53.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9529,7 +9530,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -9549,7 +9550,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>138</v>
       </c>
@@ -9560,7 +9561,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>139</v>
       </c>
@@ -9574,7 +9575,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>140</v>
       </c>
@@ -9588,7 +9589,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>141</v>
       </c>
@@ -9602,7 +9603,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>142</v>
       </c>
@@ -9616,7 +9617,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>143</v>
       </c>
@@ -9630,7 +9631,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>144</v>
       </c>
@@ -9641,7 +9642,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>145</v>
       </c>
@@ -9658,7 +9659,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>146</v>
       </c>
@@ -9675,7 +9676,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>147</v>
       </c>
@@ -9692,7 +9693,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>148</v>
       </c>
@@ -9703,7 +9704,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>149</v>
       </c>
@@ -9714,7 +9715,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>150</v>
       </c>
@@ -9731,7 +9732,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>151</v>
       </c>
@@ -9742,7 +9743,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>152</v>
       </c>
@@ -9759,7 +9760,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>153</v>
       </c>
@@ -9770,7 +9771,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>154</v>
       </c>
@@ -9781,7 +9782,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>155</v>
       </c>
@@ -9792,7 +9793,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>156</v>
       </c>
@@ -9806,7 +9807,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>157</v>
       </c>
@@ -9817,7 +9818,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>158</v>
       </c>
@@ -9828,7 +9829,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>159</v>
       </c>
@@ -9839,7 +9840,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>160</v>
       </c>
@@ -9850,7 +9851,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>161</v>
       </c>
@@ -9861,7 +9862,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>162</v>
       </c>
@@ -9878,7 +9879,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>163</v>
       </c>
@@ -9895,7 +9896,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>164</v>
       </c>
@@ -9906,7 +9907,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>165</v>
       </c>
@@ -9923,7 +9924,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>166</v>
       </c>
@@ -9940,7 +9941,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>167</v>
       </c>
@@ -9957,7 +9958,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>168</v>
       </c>
@@ -9968,7 +9969,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>169</v>
       </c>
@@ -9985,7 +9986,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>170</v>
       </c>
@@ -10002,7 +10003,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>171</v>
       </c>
@@ -10013,7 +10014,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>172</v>
       </c>
@@ -10024,7 +10025,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>173</v>
       </c>
@@ -10035,7 +10036,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>174</v>
       </c>
@@ -10052,7 +10053,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>175</v>
       </c>
@@ -10069,7 +10070,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>176</v>
       </c>
@@ -10080,7 +10081,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>177</v>
       </c>
@@ -10094,7 +10095,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>178</v>
       </c>
@@ -10108,7 +10109,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>179</v>
       </c>
@@ -10122,7 +10123,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>180</v>
       </c>
@@ -10133,7 +10134,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>181</v>
       </c>
@@ -10150,7 +10151,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>182</v>
       </c>
@@ -10161,7 +10162,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>183</v>
       </c>
@@ -10172,7 +10173,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>184</v>
       </c>
@@ -10186,7 +10187,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>185</v>
       </c>
@@ -10197,7 +10198,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>186</v>
       </c>
@@ -10208,7 +10209,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>187</v>
       </c>
@@ -10225,7 +10226,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>188</v>
       </c>
@@ -10242,7 +10243,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>189</v>
       </c>
@@ -10259,7 +10260,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>190</v>
       </c>
@@ -10276,7 +10277,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>191</v>
       </c>
@@ -10293,7 +10294,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>192</v>
       </c>
@@ -10310,7 +10311,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>193</v>
       </c>
@@ -10327,7 +10328,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>194</v>
       </c>
@@ -10341,7 +10342,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>195</v>
       </c>
@@ -10352,7 +10353,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>196</v>
       </c>
@@ -10369,7 +10370,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>197</v>
       </c>
@@ -10380,7 +10381,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>198</v>
       </c>
@@ -10391,7 +10392,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>199</v>
       </c>
@@ -10408,7 +10409,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>200</v>
       </c>
@@ -10419,7 +10420,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>201</v>
       </c>
@@ -10436,7 +10437,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>202</v>
       </c>
@@ -10453,7 +10454,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>203</v>
       </c>
@@ -10470,7 +10471,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>204</v>
       </c>
@@ -10487,7 +10488,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>205</v>
       </c>
@@ -10498,7 +10499,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>206</v>
       </c>
@@ -10509,7 +10510,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>207</v>
       </c>
@@ -10520,7 +10521,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>208</v>
       </c>
@@ -10531,7 +10532,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>209</v>
       </c>
@@ -10542,7 +10543,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>210</v>
       </c>
@@ -10553,7 +10554,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>211</v>
       </c>
@@ -10564,7 +10565,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>212</v>
       </c>
@@ -10575,7 +10576,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>213</v>
       </c>
@@ -10586,7 +10587,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>214</v>
       </c>
@@ -10597,7 +10598,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>215</v>
       </c>
@@ -10608,7 +10609,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>216</v>
       </c>
@@ -10625,7 +10626,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>217</v>
       </c>
@@ -10636,7 +10637,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>218</v>
       </c>
@@ -10647,7 +10648,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>219</v>
       </c>
@@ -10658,7 +10659,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>220</v>
       </c>
@@ -10669,7 +10670,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>221</v>
       </c>
@@ -10686,7 +10687,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>222</v>
       </c>
@@ -10697,7 +10698,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>223</v>
       </c>
@@ -10708,7 +10709,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>224</v>
       </c>
@@ -10719,7 +10720,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>225</v>
       </c>
@@ -10730,7 +10731,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>226</v>
       </c>
@@ -10741,7 +10742,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>227</v>
       </c>
@@ -10752,7 +10753,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>228</v>
       </c>
@@ -10769,7 +10770,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>229</v>
       </c>
@@ -10780,7 +10781,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>230</v>
       </c>
@@ -10797,7 +10798,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>231</v>
       </c>
@@ -10808,7 +10809,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>232</v>
       </c>
@@ -10819,7 +10820,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>233</v>
       </c>
@@ -10836,7 +10837,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>234</v>
       </c>
@@ -10847,7 +10848,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>235</v>
       </c>
@@ -10864,7 +10865,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>236</v>
       </c>
@@ -10881,7 +10882,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>237</v>
       </c>
@@ -10892,7 +10893,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>238</v>
       </c>
@@ -10903,7 +10904,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>239</v>
       </c>
@@ -10920,7 +10921,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>240</v>
       </c>
@@ -10931,7 +10932,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>241</v>
       </c>
@@ -10942,7 +10943,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>242</v>
       </c>
@@ -10953,7 +10954,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>243</v>
       </c>
@@ -10964,7 +10965,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>244</v>
       </c>
@@ -10975,7 +10976,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>245</v>
       </c>
@@ -10986,7 +10987,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>246</v>
       </c>
@@ -10997,7 +10998,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>247</v>
       </c>
@@ -11014,7 +11015,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>248</v>
       </c>
@@ -11025,7 +11026,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>249</v>
       </c>
@@ -11036,7 +11037,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>250</v>
       </c>
@@ -11053,7 +11054,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>251</v>
       </c>
@@ -11064,7 +11065,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>252</v>
       </c>
@@ -11081,7 +11082,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>253</v>
       </c>
@@ -11092,7 +11093,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>254</v>
       </c>
@@ -11103,7 +11104,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>255</v>
       </c>
@@ -11114,7 +11115,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>256</v>
       </c>
@@ -11125,7 +11126,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>257</v>
       </c>
@@ -11136,7 +11137,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>258</v>
       </c>
@@ -11147,7 +11148,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>259</v>
       </c>
@@ -11158,7 +11159,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>260</v>
       </c>
@@ -11169,7 +11170,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>261</v>
       </c>
@@ -11180,7 +11181,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>262</v>
       </c>
@@ -11191,7 +11192,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>263</v>
       </c>
@@ -11202,7 +11203,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>264</v>
       </c>
@@ -11213,7 +11214,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>265</v>
       </c>
@@ -11224,7 +11225,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>266</v>
       </c>
@@ -11235,7 +11236,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>267</v>
       </c>
@@ -11246,7 +11247,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>268</v>
       </c>
@@ -11257,7 +11258,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>269</v>
       </c>
@@ -11268,7 +11269,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>270</v>
       </c>
@@ -11279,7 +11280,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>271</v>
       </c>
@@ -11290,7 +11291,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>272</v>
       </c>
@@ -11301,7 +11302,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>273</v>
       </c>
@@ -11312,7 +11313,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>274</v>
       </c>
@@ -11323,7 +11324,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>275</v>
       </c>
@@ -11337,7 +11338,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>276</v>
       </c>
@@ -11351,7 +11352,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>277</v>
       </c>
@@ -11362,7 +11363,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>278</v>
       </c>
@@ -11373,7 +11374,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>279</v>
       </c>
@@ -11384,7 +11385,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>280</v>
       </c>
@@ -11395,7 +11396,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>281</v>
       </c>
@@ -11406,7 +11407,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>282</v>
       </c>
@@ -11417,7 +11418,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>283</v>
       </c>
@@ -11428,7 +11429,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>284</v>
       </c>
@@ -11442,7 +11443,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>285</v>
       </c>
@@ -11453,7 +11454,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>286</v>
       </c>
@@ -11467,7 +11468,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>287</v>
       </c>
@@ -11481,7 +11482,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>288</v>
       </c>
@@ -11495,7 +11496,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>289</v>
       </c>
@@ -11506,7 +11507,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>290</v>
       </c>
@@ -11517,7 +11518,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>291</v>
       </c>
@@ -11528,7 +11529,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>292</v>
       </c>
@@ -11539,7 +11540,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>293</v>
       </c>
@@ -11550,7 +11551,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>294</v>
       </c>
@@ -11564,7 +11565,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>295</v>
       </c>
@@ -11578,7 +11579,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>296</v>
       </c>
@@ -11592,7 +11593,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>297</v>
       </c>
@@ -11606,7 +11607,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>298</v>
       </c>
@@ -11620,7 +11621,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>299</v>
       </c>
@@ -11634,7 +11635,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>300</v>
       </c>
@@ -11648,7 +11649,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>301</v>
       </c>
@@ -11662,7 +11663,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>302</v>
       </c>
@@ -11676,7 +11677,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>303</v>
       </c>
@@ -11690,7 +11691,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>304</v>
       </c>
@@ -11704,7 +11705,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>305</v>
       </c>
@@ -11715,7 +11716,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>306</v>
       </c>
@@ -11729,7 +11730,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>307</v>
       </c>
@@ -11743,7 +11744,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>308</v>
       </c>
@@ -11760,7 +11761,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>309</v>
       </c>
@@ -11774,7 +11775,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>310</v>
       </c>
@@ -11788,7 +11789,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>311</v>
       </c>
@@ -11805,7 +11806,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>312</v>
       </c>
@@ -11816,7 +11817,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>313</v>
       </c>
@@ -11827,7 +11828,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>314</v>
       </c>
@@ -11841,7 +11842,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>393</v>
       </c>
@@ -11855,7 +11856,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>394</v>
       </c>
@@ -11869,7 +11870,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>395</v>
       </c>
@@ -11880,7 +11881,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>396</v>
       </c>
@@ -11894,7 +11895,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>397</v>
       </c>
@@ -11908,7 +11909,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>398</v>
       </c>
@@ -11922,7 +11923,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>399</v>
       </c>
@@ -11936,7 +11937,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>400</v>
       </c>
@@ -11950,7 +11951,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>401</v>
       </c>
@@ -11964,7 +11965,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>402</v>
       </c>
@@ -11975,7 +11976,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>403</v>
       </c>
@@ -11989,7 +11990,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>404</v>
       </c>
@@ -12003,7 +12004,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>405</v>
       </c>
@@ -12017,7 +12018,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>406</v>
       </c>
@@ -12031,7 +12032,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>407</v>
       </c>
@@ -12045,7 +12046,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>408</v>
       </c>
@@ -12059,7 +12060,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>409</v>
       </c>
@@ -12073,7 +12074,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>410</v>
       </c>
@@ -12084,7 +12085,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>411</v>
       </c>
@@ -12098,7 +12099,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>412</v>
       </c>
@@ -12112,7 +12113,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>413</v>
       </c>
@@ -12126,7 +12127,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>414</v>
       </c>
@@ -12140,7 +12141,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>415</v>
       </c>
@@ -12154,7 +12155,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>416</v>
       </c>
@@ -12165,7 +12166,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>417</v>
       </c>
@@ -12176,7 +12177,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>418</v>
       </c>
@@ -12190,7 +12191,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>419</v>
       </c>
@@ -12201,7 +12202,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>420</v>
       </c>
@@ -12218,7 +12219,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>421</v>
       </c>
@@ -12232,7 +12233,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>422</v>
       </c>
@@ -12249,7 +12250,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>423</v>
       </c>
@@ -12266,7 +12267,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>424</v>
       </c>
@@ -12277,7 +12278,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>425</v>
       </c>
@@ -12288,7 +12289,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>426</v>
       </c>
@@ -12299,7 +12300,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>427</v>
       </c>
@@ -12310,7 +12311,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>428</v>
       </c>
@@ -12321,7 +12322,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>429</v>
       </c>
@@ -12332,7 +12333,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>430</v>
       </c>
@@ -12343,7 +12344,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>431</v>
       </c>
@@ -12360,7 +12361,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>432</v>
       </c>
@@ -12371,7 +12372,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>433</v>
       </c>
@@ -12382,7 +12383,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>434</v>
       </c>
@@ -12393,7 +12394,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>435</v>
       </c>
@@ -12404,7 +12405,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>436</v>
       </c>
@@ -12415,7 +12416,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>437</v>
       </c>
@@ -12426,7 +12427,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>438</v>
       </c>
@@ -12437,7 +12438,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>439</v>
       </c>
@@ -12448,7 +12449,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>440</v>
       </c>
@@ -12459,7 +12460,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>441</v>
       </c>
@@ -12470,7 +12471,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>442</v>
       </c>
@@ -12481,7 +12482,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>443</v>
       </c>
@@ -12492,7 +12493,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>444</v>
       </c>
@@ -12503,7 +12504,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>445</v>
       </c>
@@ -12514,7 +12515,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>446</v>
       </c>
@@ -12525,7 +12526,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>447</v>
       </c>
@@ -12536,7 +12537,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>448</v>
       </c>
@@ -12553,7 +12554,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>449</v>
       </c>
@@ -12564,7 +12565,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>450</v>
       </c>
@@ -12575,7 +12576,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>451</v>
       </c>
@@ -12586,7 +12587,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>452</v>
       </c>
@@ -12597,7 +12598,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>453</v>
       </c>
@@ -12608,7 +12609,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>454</v>
       </c>
@@ -12619,7 +12620,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>455</v>
       </c>
@@ -12630,7 +12631,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>456</v>
       </c>
@@ -12644,7 +12645,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>457</v>
       </c>
@@ -12655,7 +12656,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>458</v>
       </c>
@@ -12672,7 +12673,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>459</v>
       </c>
@@ -12683,7 +12684,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>460</v>
       </c>
@@ -12691,7 +12692,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>461</v>
       </c>
@@ -12702,7 +12703,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>462</v>
       </c>
@@ -12713,7 +12714,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>463</v>
       </c>
@@ -12727,7 +12728,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>464</v>
       </c>
@@ -12738,7 +12739,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>465</v>
       </c>
@@ -12752,7 +12753,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>466</v>
       </c>
@@ -12763,7 +12764,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>467</v>
       </c>
@@ -12774,7 +12775,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>468</v>
       </c>
@@ -12785,7 +12786,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>469</v>
       </c>
@@ -12796,7 +12797,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>470</v>
       </c>
@@ -12807,7 +12808,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>471</v>
       </c>
@@ -12821,7 +12822,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>472</v>
       </c>
@@ -12835,7 +12836,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>473</v>
       </c>
@@ -12846,7 +12847,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>474</v>
       </c>
@@ -12857,7 +12858,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>475</v>
       </c>
@@ -12868,7 +12869,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>476</v>
       </c>
@@ -12879,7 +12880,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>477</v>
       </c>
@@ -12890,7 +12891,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>478</v>
       </c>
@@ -12907,7 +12908,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>479</v>
       </c>
@@ -12924,7 +12925,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>480</v>
       </c>
@@ -12941,7 +12942,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>481</v>
       </c>
@@ -12958,7 +12959,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>482</v>
       </c>
@@ -12969,7 +12970,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>483</v>
       </c>
@@ -12980,7 +12981,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>484</v>
       </c>
@@ -12991,7 +12992,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>485</v>
       </c>
@@ -13002,7 +13003,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>486</v>
       </c>
@@ -13013,7 +13014,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>487</v>
       </c>
@@ -13030,7 +13031,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>488</v>
       </c>
@@ -13041,7 +13042,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>489</v>
       </c>
@@ -13052,7 +13053,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>490</v>
       </c>
@@ -13063,7 +13064,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>491</v>
       </c>
@@ -13074,7 +13075,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>492</v>
       </c>
@@ -13085,7 +13086,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>493</v>
       </c>
@@ -13096,7 +13097,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>494</v>
       </c>
@@ -13107,7 +13108,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>495</v>
       </c>
@@ -13118,7 +13119,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>496</v>
       </c>
@@ -13129,7 +13130,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>497</v>
       </c>
@@ -13140,7 +13141,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>498</v>
       </c>
@@ -13151,7 +13152,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>499</v>
       </c>
@@ -13162,7 +13163,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>500</v>
       </c>
@@ -13173,7 +13174,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>501</v>
       </c>
@@ -13184,7 +13185,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>502</v>
       </c>
@@ -13195,7 +13196,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>503</v>
       </c>
@@ -13206,7 +13207,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>504</v>
       </c>
@@ -13220,7 +13221,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>505</v>
       </c>
@@ -13231,7 +13232,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>506</v>
       </c>
@@ -13242,7 +13243,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>507</v>
       </c>
@@ -13253,7 +13254,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>508</v>
       </c>
@@ -13267,7 +13268,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>509</v>
       </c>
@@ -13278,7 +13279,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>510</v>
       </c>
@@ -13289,7 +13290,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>511</v>
       </c>
@@ -13300,7 +13301,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>512</v>
       </c>
@@ -13317,7 +13318,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>513</v>
       </c>
@@ -13328,7 +13329,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>514</v>
       </c>
@@ -13342,7 +13343,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>515</v>
       </c>
@@ -13353,7 +13354,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>516</v>
       </c>
@@ -13364,7 +13365,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>517</v>
       </c>
@@ -13375,7 +13376,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>518</v>
       </c>
@@ -13392,7 +13393,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>519</v>
       </c>
@@ -13406,7 +13407,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>520</v>
       </c>
@@ -13420,7 +13421,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>521</v>
       </c>
@@ -13431,7 +13432,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>522</v>
       </c>
@@ -13445,7 +13446,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>523</v>
       </c>
@@ -13456,7 +13457,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>524</v>
       </c>
@@ -13473,7 +13474,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>525</v>
       </c>
@@ -13490,7 +13491,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>526</v>
       </c>
@@ -13507,7 +13508,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>527</v>
       </c>
@@ -13518,7 +13519,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>528</v>
       </c>
@@ -13529,7 +13530,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>529</v>
       </c>
@@ -13540,7 +13541,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>530</v>
       </c>
@@ -13557,7 +13558,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>531</v>
       </c>
@@ -13568,7 +13569,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>532</v>
       </c>
@@ -13579,7 +13580,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>533</v>
       </c>
@@ -13593,7 +13594,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>534</v>
       </c>
@@ -13604,7 +13605,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>535</v>
       </c>
@@ -13621,7 +13622,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>536</v>
       </c>
@@ -13638,7 +13639,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>537</v>
       </c>
@@ -13649,7 +13650,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>538</v>
       </c>
@@ -13660,7 +13661,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>539</v>
       </c>
@@ -13671,7 +13672,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>540</v>
       </c>
@@ -13685,7 +13686,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>541</v>
       </c>
@@ -13696,7 +13697,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>542</v>
       </c>
@@ -13707,7 +13708,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>543</v>
       </c>
@@ -13724,7 +13725,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>544</v>
       </c>
@@ -13735,7 +13736,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>545</v>
       </c>
@@ -13746,7 +13747,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>546</v>
       </c>
@@ -13757,7 +13758,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>547</v>
       </c>
@@ -13768,7 +13769,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>548</v>
       </c>
@@ -13785,7 +13786,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>549</v>
       </c>
@@ -13802,7 +13803,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>550</v>
       </c>
@@ -13813,7 +13814,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>551</v>
       </c>
@@ -13824,7 +13825,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>552</v>
       </c>
@@ -13835,7 +13836,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>553</v>
       </c>
@@ -13846,7 +13847,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>554</v>
       </c>
@@ -13857,7 +13858,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>555</v>
       </c>
@@ -13868,7 +13869,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>556</v>
       </c>
@@ -13882,7 +13883,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>557</v>
       </c>
@@ -13893,7 +13894,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>558</v>
       </c>
@@ -13904,7 +13905,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>559</v>
       </c>
@@ -13921,7 +13922,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>560</v>
       </c>
@@ -13932,7 +13933,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>561</v>
       </c>
@@ -13943,7 +13944,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>562</v>
       </c>
@@ -13960,7 +13961,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>563</v>
       </c>
@@ -13971,7 +13972,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>564</v>
       </c>
@@ -13985,7 +13986,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>565</v>
       </c>
@@ -13996,7 +13997,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>566</v>
       </c>
@@ -14007,7 +14008,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>567</v>
       </c>
@@ -14018,7 +14019,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>568</v>
       </c>
@@ -14029,7 +14030,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>569</v>
       </c>
@@ -14043,7 +14044,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>570</v>
       </c>
@@ -14054,7 +14055,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>571</v>
       </c>
@@ -14065,7 +14066,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>572</v>
       </c>
@@ -14079,7 +14080,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>573</v>
       </c>
@@ -14090,7 +14091,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>574</v>
       </c>
@@ -14107,7 +14108,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>575</v>
       </c>
@@ -14118,7 +14119,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>576</v>
       </c>
@@ -14129,7 +14130,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>577</v>
       </c>
@@ -14140,7 +14141,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>578</v>
       </c>
@@ -14151,7 +14152,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>579</v>
       </c>
@@ -14162,7 +14163,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>580</v>
       </c>
@@ -14176,7 +14177,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>581</v>
       </c>
@@ -14187,7 +14188,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>582</v>
       </c>
@@ -14198,7 +14199,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>583</v>
       </c>
@@ -14209,7 +14210,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>584</v>
       </c>
@@ -14220,7 +14221,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>585</v>
       </c>
@@ -14234,7 +14235,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>586</v>
       </c>
@@ -14245,7 +14246,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>587</v>
       </c>
@@ -14262,7 +14263,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>588</v>
       </c>
@@ -14276,7 +14277,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>589</v>
       </c>
@@ -14290,7 +14291,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>590</v>
       </c>
@@ -14301,7 +14302,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>591</v>
       </c>
@@ -14318,7 +14319,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>592</v>
       </c>
@@ -14329,7 +14330,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>593</v>
       </c>
@@ -14340,7 +14341,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>594</v>
       </c>
@@ -14351,7 +14352,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>595</v>
       </c>
@@ -14362,7 +14363,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>596</v>
       </c>
@@ -14379,7 +14380,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>597</v>
       </c>
@@ -14396,7 +14397,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>598</v>
       </c>
@@ -14413,7 +14414,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>599</v>
       </c>
@@ -14424,7 +14425,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>600</v>
       </c>
@@ -14435,7 +14436,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>601</v>
       </c>
@@ -14449,7 +14450,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>602</v>
       </c>
@@ -14463,7 +14464,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>603</v>
       </c>
@@ -14474,7 +14475,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>604</v>
       </c>
@@ -14488,7 +14489,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>605</v>
       </c>
@@ -14499,7 +14500,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>606</v>
       </c>
@@ -14510,7 +14511,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>607</v>
       </c>
@@ -14524,7 +14525,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>608</v>
       </c>
@@ -14535,7 +14536,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>609</v>
       </c>
@@ -14549,7 +14550,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>610</v>
       </c>
@@ -14566,7 +14567,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>611</v>
       </c>
@@ -14577,7 +14578,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>612</v>
       </c>
@@ -14588,7 +14589,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>613</v>
       </c>

--- a/FlowTracker.xlsx
+++ b/FlowTracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A85CAB-2A17-4317-A213-FE266235E01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155AB9B2-186A-4732-A2ED-A7E038D1C422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterSheet" sheetId="9" r:id="rId1"/>
@@ -23,7 +23,6 @@
     <sheet name="PulmArtOld" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -3190,9 +3189,6 @@
     <t>0;126;126;0;0.955;0</t>
   </si>
   <si>
-    <t>1;28;28;0;1;0</t>
-  </si>
-  <si>
     <t>3;11;11;0;37.90;0</t>
   </si>
   <si>
@@ -3556,13 +3552,16 @@
     <t>11;55;57;59;19.31;AA</t>
   </si>
   <si>
-    <t>26;100;103;0;5.14;AB</t>
-  </si>
-  <si>
-    <t>27;101;102;0;5.14;AC</t>
-  </si>
-  <si>
     <t>126;98;99;0;0;AD</t>
+  </si>
+  <si>
+    <t>26;100;103;0;6.12;AB</t>
+  </si>
+  <si>
+    <t>27;101;102;0;6.12;AC</t>
+  </si>
+  <si>
+    <t>1;28;28;0;0.955;0</t>
   </si>
 </sst>
 </file>
@@ -4022,7 +4021,7 @@
         <v>935</v>
       </c>
       <c r="B3" t="s">
-        <v>1048</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4030,7 +4029,7 @@
         <v>817</v>
       </c>
       <c r="B4" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4038,7 +4037,7 @@
         <v>844</v>
       </c>
       <c r="B5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4046,7 +4045,7 @@
         <v>845</v>
       </c>
       <c r="B6" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4054,7 +4053,7 @@
         <v>818</v>
       </c>
       <c r="B7" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4062,7 +4061,7 @@
         <v>807</v>
       </c>
       <c r="B8" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4070,7 +4069,7 @@
         <v>819</v>
       </c>
       <c r="B9" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -4078,7 +4077,7 @@
         <v>846</v>
       </c>
       <c r="B10" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -4086,7 +4085,7 @@
         <v>811</v>
       </c>
       <c r="B11" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4094,7 +4093,7 @@
         <v>848</v>
       </c>
       <c r="B12" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -4102,7 +4101,7 @@
         <v>847</v>
       </c>
       <c r="B13" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -4110,7 +4109,7 @@
         <v>1007</v>
       </c>
       <c r="B14" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -4118,7 +4117,7 @@
         <v>1008</v>
       </c>
       <c r="B15" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -4126,7 +4125,7 @@
         <v>1009</v>
       </c>
       <c r="B16" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -4134,7 +4133,7 @@
         <v>1010</v>
       </c>
       <c r="B17" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -4142,7 +4141,7 @@
         <v>1022</v>
       </c>
       <c r="B18" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -4150,7 +4149,7 @@
         <v>1011</v>
       </c>
       <c r="B19" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -4158,7 +4157,7 @@
         <v>1014</v>
       </c>
       <c r="B20" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -4166,7 +4165,7 @@
         <v>1015</v>
       </c>
       <c r="B21" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -4174,7 +4173,7 @@
         <v>1016</v>
       </c>
       <c r="B22" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -4182,7 +4181,7 @@
         <v>1017</v>
       </c>
       <c r="B23" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -4190,7 +4189,7 @@
         <v>1018</v>
       </c>
       <c r="B24" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -4198,7 +4197,7 @@
         <v>1019</v>
       </c>
       <c r="B25" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -4206,7 +4205,7 @@
         <v>1020</v>
       </c>
       <c r="B26" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -4214,7 +4213,7 @@
         <v>1021</v>
       </c>
       <c r="B27" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -4246,7 +4245,7 @@
         <v>964</v>
       </c>
       <c r="B31" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -4254,7 +4253,7 @@
         <v>965</v>
       </c>
       <c r="B32" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -4262,7 +4261,7 @@
         <v>966</v>
       </c>
       <c r="B33" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -4270,7 +4269,7 @@
         <v>967</v>
       </c>
       <c r="B34" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -4278,7 +4277,7 @@
         <v>968</v>
       </c>
       <c r="B35" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -4286,7 +4285,7 @@
         <v>969</v>
       </c>
       <c r="B36" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -4294,7 +4293,7 @@
         <v>970</v>
       </c>
       <c r="B37" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -4302,7 +4301,7 @@
         <v>971</v>
       </c>
       <c r="B38" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -4310,7 +4309,7 @@
         <v>972</v>
       </c>
       <c r="B39" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -4318,7 +4317,7 @@
         <v>973</v>
       </c>
       <c r="B40" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -4326,7 +4325,7 @@
         <v>974</v>
       </c>
       <c r="B41" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -4334,7 +4333,7 @@
         <v>975</v>
       </c>
       <c r="B42" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -4342,7 +4341,7 @@
         <v>976</v>
       </c>
       <c r="B43" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -4350,7 +4349,7 @@
         <v>977</v>
       </c>
       <c r="B44" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -4358,7 +4357,7 @@
         <v>978</v>
       </c>
       <c r="B45" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -4366,7 +4365,7 @@
         <v>979</v>
       </c>
       <c r="B46" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -4374,7 +4373,7 @@
         <v>980</v>
       </c>
       <c r="B47" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -4382,7 +4381,7 @@
         <v>981</v>
       </c>
       <c r="B48" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -4390,7 +4389,7 @@
         <v>982</v>
       </c>
       <c r="B49" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -4398,7 +4397,7 @@
         <v>983</v>
       </c>
       <c r="B50" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -4406,7 +4405,7 @@
         <v>984</v>
       </c>
       <c r="B51" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -4414,7 +4413,7 @@
         <v>985</v>
       </c>
       <c r="B52" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -4422,7 +4421,7 @@
         <v>986</v>
       </c>
       <c r="B53" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -4430,7 +4429,7 @@
         <v>987</v>
       </c>
       <c r="B54" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -4438,7 +4437,7 @@
         <v>937</v>
       </c>
       <c r="B55" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -4446,7 +4445,7 @@
         <v>938</v>
       </c>
       <c r="B56" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -4454,7 +4453,7 @@
         <v>939</v>
       </c>
       <c r="B57" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -4462,7 +4461,7 @@
         <v>940</v>
       </c>
       <c r="B58" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -4470,7 +4469,7 @@
         <v>941</v>
       </c>
       <c r="B59" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -4478,7 +4477,7 @@
         <v>942</v>
       </c>
       <c r="B60" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -4486,7 +4485,7 @@
         <v>943</v>
       </c>
       <c r="B61" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -4494,7 +4493,7 @@
         <v>944</v>
       </c>
       <c r="B62" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -4502,7 +4501,7 @@
         <v>945</v>
       </c>
       <c r="B63" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -4510,7 +4509,7 @@
         <v>946</v>
       </c>
       <c r="B64" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -4518,7 +4517,7 @@
         <v>947</v>
       </c>
       <c r="B65" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -4526,7 +4525,7 @@
         <v>948</v>
       </c>
       <c r="B66" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -4534,7 +4533,7 @@
         <v>949</v>
       </c>
       <c r="B67" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -4542,7 +4541,7 @@
         <v>950</v>
       </c>
       <c r="B68" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -4550,7 +4549,7 @@
         <v>951</v>
       </c>
       <c r="B69" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -4558,7 +4557,7 @@
         <v>952</v>
       </c>
       <c r="B70" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -4566,7 +4565,7 @@
         <v>953</v>
       </c>
       <c r="B71" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -4574,7 +4573,7 @@
         <v>954</v>
       </c>
       <c r="B72" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -4582,7 +4581,7 @@
         <v>955</v>
       </c>
       <c r="B73" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -4590,7 +4589,7 @@
         <v>956</v>
       </c>
       <c r="B74" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -4598,7 +4597,7 @@
         <v>957</v>
       </c>
       <c r="B75" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -4606,7 +4605,7 @@
         <v>958</v>
       </c>
       <c r="B76" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -4614,7 +4613,7 @@
         <v>959</v>
       </c>
       <c r="B77" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -4622,7 +4621,7 @@
         <v>960</v>
       </c>
       <c r="B78" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -4630,7 +4629,7 @@
         <v>961</v>
       </c>
       <c r="B79" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -4638,7 +4637,7 @@
         <v>962</v>
       </c>
       <c r="B80" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -4646,7 +4645,7 @@
         <v>988</v>
       </c>
       <c r="B81" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -4654,7 +4653,7 @@
         <v>989</v>
       </c>
       <c r="B82" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -4662,7 +4661,7 @@
         <v>990</v>
       </c>
       <c r="B83" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -4670,7 +4669,7 @@
         <v>991</v>
       </c>
       <c r="B84" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -4678,7 +4677,7 @@
         <v>992</v>
       </c>
       <c r="B85" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -4686,7 +4685,7 @@
         <v>993</v>
       </c>
       <c r="B86" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -4694,7 +4693,7 @@
         <v>994</v>
       </c>
       <c r="B87" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -4702,7 +4701,7 @@
         <v>995</v>
       </c>
       <c r="B88" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -4710,7 +4709,7 @@
         <v>996</v>
       </c>
       <c r="B89" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -4718,7 +4717,7 @@
         <v>997</v>
       </c>
       <c r="B90" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -4726,7 +4725,7 @@
         <v>998</v>
       </c>
       <c r="B91" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -4734,7 +4733,7 @@
         <v>999</v>
       </c>
       <c r="B92" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -4742,7 +4741,7 @@
         <v>1000</v>
       </c>
       <c r="B93" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -4750,7 +4749,7 @@
         <v>1001</v>
       </c>
       <c r="B94" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -4758,7 +4757,7 @@
         <v>1002</v>
       </c>
       <c r="B95" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -4766,7 +4765,7 @@
         <v>1003</v>
       </c>
       <c r="B96" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -4774,7 +4773,7 @@
         <v>1004</v>
       </c>
       <c r="B97" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -4782,7 +4781,7 @@
         <v>1005</v>
       </c>
       <c r="B98" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -4790,7 +4789,7 @@
         <v>1006</v>
       </c>
       <c r="B99" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -4798,7 +4797,7 @@
         <v>140</v>
       </c>
       <c r="B100" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -4806,7 +4805,7 @@
         <v>927</v>
       </c>
       <c r="B101" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -4814,7 +4813,7 @@
         <v>928</v>
       </c>
       <c r="B102" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -4822,7 +4821,7 @@
         <v>929</v>
       </c>
       <c r="B103" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -4830,7 +4829,7 @@
         <v>930</v>
       </c>
       <c r="B104" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -4838,7 +4837,7 @@
         <v>931</v>
       </c>
       <c r="B105" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -4846,7 +4845,7 @@
         <v>1023</v>
       </c>
       <c r="B106" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -4854,7 +4853,7 @@
         <v>1024</v>
       </c>
       <c r="B107" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -4862,7 +4861,7 @@
         <v>1025</v>
       </c>
       <c r="B108" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -4870,7 +4869,7 @@
         <v>1026</v>
       </c>
       <c r="B109" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -4878,7 +4877,7 @@
         <v>1027</v>
       </c>
       <c r="B110" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -4886,7 +4885,7 @@
         <v>1028</v>
       </c>
       <c r="B111" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -4894,7 +4893,7 @@
         <v>1029</v>
       </c>
       <c r="B112" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -4902,7 +4901,7 @@
         <v>1030</v>
       </c>
       <c r="B113" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -4910,7 +4909,7 @@
         <v>1031</v>
       </c>
       <c r="B114" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -4918,7 +4917,7 @@
         <v>1032</v>
       </c>
       <c r="B115" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -4926,7 +4925,7 @@
         <v>1033</v>
       </c>
       <c r="B116" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -4934,7 +4933,7 @@
         <v>1034</v>
       </c>
       <c r="B117" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -4942,7 +4941,7 @@
         <v>1035</v>
       </c>
       <c r="B118" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -4950,7 +4949,7 @@
         <v>1036</v>
       </c>
       <c r="B119" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -4958,7 +4957,7 @@
         <v>1037</v>
       </c>
       <c r="B120" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -4966,7 +4965,7 @@
         <v>1038</v>
       </c>
       <c r="B121" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -4974,7 +4973,7 @@
         <v>1039</v>
       </c>
       <c r="B122" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -4982,7 +4981,7 @@
         <v>1040</v>
       </c>
       <c r="B123" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -4990,7 +4989,7 @@
         <v>1041</v>
       </c>
       <c r="B124" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -4998,7 +4997,7 @@
         <v>1042</v>
       </c>
       <c r="B125" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -5006,7 +5005,7 @@
         <v>1043</v>
       </c>
       <c r="B126" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -5014,7 +5013,7 @@
         <v>1044</v>
       </c>
       <c r="B127" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -5022,7 +5021,7 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
     </row>
   </sheetData>
@@ -9395,18 +9394,19 @@
         <v>934</v>
       </c>
       <c r="B19">
-        <v>10.5</v>
+        <f>10.5+2</f>
+        <v>12.5</v>
       </c>
       <c r="C19">
         <v>100</v>
       </c>
       <c r="D19">
         <f t="shared" ref="D19" si="6">($H$2*B19)/($I$2*C19)</f>
-        <v>8.5615384615384621E-2</v>
+        <v>0.10192307692307692</v>
       </c>
       <c r="E19" s="5">
         <f t="shared" ref="E19" si="7">D19*60</f>
-        <v>5.1369230769230771</v>
+        <v>6.115384615384615</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">

--- a/FlowTracker.xlsx
+++ b/FlowTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155AB9B2-186A-4732-A2ED-A7E038D1C422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B60E3F-45C6-42DB-B854-4F9796DF9628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3309,9 +3309,6 @@
     <t>47;104;105;0;0;O</t>
   </si>
   <si>
-    <t>48;5;5;0;0;0</t>
-  </si>
-  <si>
     <t>49;12;12;0;0;0</t>
   </si>
   <si>
@@ -3480,9 +3477,6 @@
     <t>104;7;7;0;0;0</t>
   </si>
   <si>
-    <t>105;10;10;0;0;0</t>
-  </si>
-  <si>
     <t>106;13;13;0;0;0</t>
   </si>
   <si>
@@ -3562,6 +3556,12 @@
   </si>
   <si>
     <t>1;28;28;0;0.955;0</t>
+  </si>
+  <si>
+    <t>48;10;10;0;0;0</t>
+  </si>
+  <si>
+    <t>105;5;5;0;0;0</t>
   </si>
 </sst>
 </file>
@@ -4021,7 +4021,7 @@
         <v>935</v>
       </c>
       <c r="B3" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4029,7 +4029,7 @@
         <v>817</v>
       </c>
       <c r="B4" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4093,7 +4093,7 @@
         <v>848</v>
       </c>
       <c r="B12" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -4101,7 +4101,7 @@
         <v>847</v>
       </c>
       <c r="B13" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -4221,7 +4221,7 @@
         <v>1012</v>
       </c>
       <c r="B28" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -4229,7 +4229,7 @@
         <v>1013</v>
       </c>
       <c r="B29" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -4397,7 +4397,7 @@
         <v>983</v>
       </c>
       <c r="B50" t="s">
-        <v>1088</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -4405,7 +4405,7 @@
         <v>984</v>
       </c>
       <c r="B51" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -4413,7 +4413,7 @@
         <v>985</v>
       </c>
       <c r="B52" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -4421,7 +4421,7 @@
         <v>986</v>
       </c>
       <c r="B53" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -4429,7 +4429,7 @@
         <v>987</v>
       </c>
       <c r="B54" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -4437,7 +4437,7 @@
         <v>937</v>
       </c>
       <c r="B55" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -4445,7 +4445,7 @@
         <v>938</v>
       </c>
       <c r="B56" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -4453,7 +4453,7 @@
         <v>939</v>
       </c>
       <c r="B57" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -4461,7 +4461,7 @@
         <v>940</v>
       </c>
       <c r="B58" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -4469,7 +4469,7 @@
         <v>941</v>
       </c>
       <c r="B59" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -4477,7 +4477,7 @@
         <v>942</v>
       </c>
       <c r="B60" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -4485,7 +4485,7 @@
         <v>943</v>
       </c>
       <c r="B61" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -4493,7 +4493,7 @@
         <v>944</v>
       </c>
       <c r="B62" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -4501,7 +4501,7 @@
         <v>945</v>
       </c>
       <c r="B63" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -4509,7 +4509,7 @@
         <v>946</v>
       </c>
       <c r="B64" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -4517,7 +4517,7 @@
         <v>947</v>
       </c>
       <c r="B65" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -4525,7 +4525,7 @@
         <v>948</v>
       </c>
       <c r="B66" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -4533,7 +4533,7 @@
         <v>949</v>
       </c>
       <c r="B67" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -4541,7 +4541,7 @@
         <v>950</v>
       </c>
       <c r="B68" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -4549,7 +4549,7 @@
         <v>951</v>
       </c>
       <c r="B69" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -4557,7 +4557,7 @@
         <v>952</v>
       </c>
       <c r="B70" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -4565,7 +4565,7 @@
         <v>953</v>
       </c>
       <c r="B71" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -4573,7 +4573,7 @@
         <v>954</v>
       </c>
       <c r="B72" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -4581,7 +4581,7 @@
         <v>955</v>
       </c>
       <c r="B73" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -4589,7 +4589,7 @@
         <v>956</v>
       </c>
       <c r="B74" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -4597,7 +4597,7 @@
         <v>957</v>
       </c>
       <c r="B75" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -4605,7 +4605,7 @@
         <v>958</v>
       </c>
       <c r="B76" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -4613,7 +4613,7 @@
         <v>959</v>
       </c>
       <c r="B77" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -4621,7 +4621,7 @@
         <v>960</v>
       </c>
       <c r="B78" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -4629,7 +4629,7 @@
         <v>961</v>
       </c>
       <c r="B79" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -4637,7 +4637,7 @@
         <v>962</v>
       </c>
       <c r="B80" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -4645,7 +4645,7 @@
         <v>988</v>
       </c>
       <c r="B81" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -4653,7 +4653,7 @@
         <v>989</v>
       </c>
       <c r="B82" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -4661,7 +4661,7 @@
         <v>990</v>
       </c>
       <c r="B83" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -4669,7 +4669,7 @@
         <v>991</v>
       </c>
       <c r="B84" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -4677,7 +4677,7 @@
         <v>992</v>
       </c>
       <c r="B85" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -4685,7 +4685,7 @@
         <v>993</v>
       </c>
       <c r="B86" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -4693,7 +4693,7 @@
         <v>994</v>
       </c>
       <c r="B87" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -4701,7 +4701,7 @@
         <v>995</v>
       </c>
       <c r="B88" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -4709,7 +4709,7 @@
         <v>996</v>
       </c>
       <c r="B89" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -4717,7 +4717,7 @@
         <v>997</v>
       </c>
       <c r="B90" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -4725,7 +4725,7 @@
         <v>998</v>
       </c>
       <c r="B91" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -4733,7 +4733,7 @@
         <v>999</v>
       </c>
       <c r="B92" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -4741,7 +4741,7 @@
         <v>1000</v>
       </c>
       <c r="B93" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -4749,7 +4749,7 @@
         <v>1001</v>
       </c>
       <c r="B94" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -4757,7 +4757,7 @@
         <v>1002</v>
       </c>
       <c r="B95" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -4765,7 +4765,7 @@
         <v>1003</v>
       </c>
       <c r="B96" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -4773,7 +4773,7 @@
         <v>1004</v>
       </c>
       <c r="B97" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -4781,7 +4781,7 @@
         <v>1005</v>
       </c>
       <c r="B98" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -4789,7 +4789,7 @@
         <v>1006</v>
       </c>
       <c r="B99" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -4797,7 +4797,7 @@
         <v>140</v>
       </c>
       <c r="B100" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -4805,7 +4805,7 @@
         <v>927</v>
       </c>
       <c r="B101" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -4813,7 +4813,7 @@
         <v>928</v>
       </c>
       <c r="B102" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -4821,7 +4821,7 @@
         <v>929</v>
       </c>
       <c r="B103" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -4829,7 +4829,7 @@
         <v>930</v>
       </c>
       <c r="B104" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -4837,7 +4837,7 @@
         <v>931</v>
       </c>
       <c r="B105" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -4845,7 +4845,7 @@
         <v>1023</v>
       </c>
       <c r="B106" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -4853,7 +4853,7 @@
         <v>1024</v>
       </c>
       <c r="B107" t="s">
-        <v>1145</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -4861,7 +4861,7 @@
         <v>1025</v>
       </c>
       <c r="B108" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -4869,7 +4869,7 @@
         <v>1026</v>
       </c>
       <c r="B109" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -4877,7 +4877,7 @@
         <v>1027</v>
       </c>
       <c r="B110" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -4885,7 +4885,7 @@
         <v>1028</v>
       </c>
       <c r="B111" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -4893,7 +4893,7 @@
         <v>1029</v>
       </c>
       <c r="B112" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -4901,7 +4901,7 @@
         <v>1030</v>
       </c>
       <c r="B113" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -4909,7 +4909,7 @@
         <v>1031</v>
       </c>
       <c r="B114" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -4917,7 +4917,7 @@
         <v>1032</v>
       </c>
       <c r="B115" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -4925,7 +4925,7 @@
         <v>1033</v>
       </c>
       <c r="B116" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -4933,7 +4933,7 @@
         <v>1034</v>
       </c>
       <c r="B117" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -4941,7 +4941,7 @@
         <v>1035</v>
       </c>
       <c r="B118" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -4949,7 +4949,7 @@
         <v>1036</v>
       </c>
       <c r="B119" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -4957,7 +4957,7 @@
         <v>1037</v>
       </c>
       <c r="B120" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -4965,7 +4965,7 @@
         <v>1038</v>
       </c>
       <c r="B121" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -4973,7 +4973,7 @@
         <v>1039</v>
       </c>
       <c r="B122" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -4981,7 +4981,7 @@
         <v>1040</v>
       </c>
       <c r="B123" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -4989,7 +4989,7 @@
         <v>1041</v>
       </c>
       <c r="B124" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -4997,7 +4997,7 @@
         <v>1042</v>
       </c>
       <c r="B125" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -5005,7 +5005,7 @@
         <v>1043</v>
       </c>
       <c r="B126" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -5013,7 +5013,7 @@
         <v>1044</v>
       </c>
       <c r="B127" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -5021,7 +5021,7 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
   </sheetData>

--- a/FlowTracker.xlsx
+++ b/FlowTracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\PHSAhome2.phsabc.ehcnet.ca\Cassidy.Northway\Remote Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B60E3F-45C6-42DB-B854-4F9796DF9628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F747B25-5EFF-4E6C-AC10-EB10999844A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4770" windowWidth="18240" windowHeight="28440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterSheet" sheetId="9" r:id="rId1"/>

--- a/FlowTracker.xlsx
+++ b/FlowTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\PHSAhome2.phsabc.ehcnet.ca\Cassidy.Northway\Remote Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F747B25-5EFF-4E6C-AC10-EB10999844A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F222552E-8A28-4ECE-AD8C-BF9319FA0DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-4770" windowWidth="18240" windowHeight="28440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3189,27 +3189,12 @@
     <t>0;126;126;0;0.955;0</t>
   </si>
   <si>
-    <t>3;11;11;0;37.90;0</t>
-  </si>
-  <si>
-    <t>4;11;11;0;29.35;0</t>
-  </si>
-  <si>
-    <t>5;11;11;0;68.23;0</t>
-  </si>
-  <si>
     <t>6;63;63;0;5.15;0</t>
   </si>
   <si>
-    <t>7;11;11;0;42.14;0</t>
-  </si>
-  <si>
     <t>29;31;32;0;0;C</t>
   </si>
   <si>
-    <t>8;11;11;0;46.22;0</t>
-  </si>
-  <si>
     <t>9;61;61;0;5.15;0</t>
   </si>
   <si>
@@ -3562,6 +3547,21 @@
   </si>
   <si>
     <t>105;5;5;0;0;0</t>
+  </si>
+  <si>
+    <t>3;11;11;0;18.59;0</t>
+  </si>
+  <si>
+    <t>4;11;11;0;29.36;0</t>
+  </si>
+  <si>
+    <t>5;11;11;0;48.92;0</t>
+  </si>
+  <si>
+    <t>7;11;11;0;22.83;0</t>
+  </si>
+  <si>
+    <t>8;11;11;0;26.91;0</t>
   </si>
 </sst>
 </file>
@@ -4021,7 +4021,7 @@
         <v>935</v>
       </c>
       <c r="B3" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4029,7 +4029,7 @@
         <v>817</v>
       </c>
       <c r="B4" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4037,7 +4037,7 @@
         <v>844</v>
       </c>
       <c r="B5" t="s">
-        <v>1048</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
         <v>845</v>
       </c>
       <c r="B6" t="s">
-        <v>1049</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4053,7 +4053,7 @@
         <v>818</v>
       </c>
       <c r="B7" t="s">
-        <v>1050</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4061,7 +4061,7 @@
         <v>807</v>
       </c>
       <c r="B8" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4069,7 +4069,7 @@
         <v>819</v>
       </c>
       <c r="B9" t="s">
-        <v>1052</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -4077,7 +4077,7 @@
         <v>846</v>
       </c>
       <c r="B10" t="s">
-        <v>1054</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -4085,7 +4085,7 @@
         <v>811</v>
       </c>
       <c r="B11" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4093,7 +4093,7 @@
         <v>848</v>
       </c>
       <c r="B12" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -4101,7 +4101,7 @@
         <v>847</v>
       </c>
       <c r="B13" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -4109,7 +4109,7 @@
         <v>1007</v>
       </c>
       <c r="B14" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -4117,7 +4117,7 @@
         <v>1008</v>
       </c>
       <c r="B15" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -4125,7 +4125,7 @@
         <v>1009</v>
       </c>
       <c r="B16" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -4133,7 +4133,7 @@
         <v>1010</v>
       </c>
       <c r="B17" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -4141,7 +4141,7 @@
         <v>1022</v>
       </c>
       <c r="B18" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -4149,7 +4149,7 @@
         <v>1011</v>
       </c>
       <c r="B19" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -4157,7 +4157,7 @@
         <v>1014</v>
       </c>
       <c r="B20" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -4165,7 +4165,7 @@
         <v>1015</v>
       </c>
       <c r="B21" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -4173,7 +4173,7 @@
         <v>1016</v>
       </c>
       <c r="B22" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -4181,7 +4181,7 @@
         <v>1017</v>
       </c>
       <c r="B23" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -4189,7 +4189,7 @@
         <v>1018</v>
       </c>
       <c r="B24" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -4197,7 +4197,7 @@
         <v>1019</v>
       </c>
       <c r="B25" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
         <v>1020</v>
       </c>
       <c r="B26" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -4213,7 +4213,7 @@
         <v>1021</v>
       </c>
       <c r="B27" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -4221,7 +4221,7 @@
         <v>1012</v>
       </c>
       <c r="B28" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -4229,7 +4229,7 @@
         <v>1013</v>
       </c>
       <c r="B29" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -4245,7 +4245,7 @@
         <v>964</v>
       </c>
       <c r="B31" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -4253,7 +4253,7 @@
         <v>965</v>
       </c>
       <c r="B32" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -4261,7 +4261,7 @@
         <v>966</v>
       </c>
       <c r="B33" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -4269,7 +4269,7 @@
         <v>967</v>
       </c>
       <c r="B34" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -4277,7 +4277,7 @@
         <v>968</v>
       </c>
       <c r="B35" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -4285,7 +4285,7 @@
         <v>969</v>
       </c>
       <c r="B36" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -4293,7 +4293,7 @@
         <v>970</v>
       </c>
       <c r="B37" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -4301,7 +4301,7 @@
         <v>971</v>
       </c>
       <c r="B38" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -4309,7 +4309,7 @@
         <v>972</v>
       </c>
       <c r="B39" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -4317,7 +4317,7 @@
         <v>973</v>
       </c>
       <c r="B40" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -4325,7 +4325,7 @@
         <v>974</v>
       </c>
       <c r="B41" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -4333,7 +4333,7 @@
         <v>975</v>
       </c>
       <c r="B42" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -4341,7 +4341,7 @@
         <v>976</v>
       </c>
       <c r="B43" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -4349,7 +4349,7 @@
         <v>977</v>
       </c>
       <c r="B44" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -4357,7 +4357,7 @@
         <v>978</v>
       </c>
       <c r="B45" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -4365,7 +4365,7 @@
         <v>979</v>
       </c>
       <c r="B46" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -4373,7 +4373,7 @@
         <v>980</v>
       </c>
       <c r="B47" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -4381,7 +4381,7 @@
         <v>981</v>
       </c>
       <c r="B48" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -4389,7 +4389,7 @@
         <v>982</v>
       </c>
       <c r="B49" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -4397,7 +4397,7 @@
         <v>983</v>
       </c>
       <c r="B50" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -4405,7 +4405,7 @@
         <v>984</v>
       </c>
       <c r="B51" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -4413,7 +4413,7 @@
         <v>985</v>
       </c>
       <c r="B52" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -4421,7 +4421,7 @@
         <v>986</v>
       </c>
       <c r="B53" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -4429,7 +4429,7 @@
         <v>987</v>
       </c>
       <c r="B54" t="s">
-        <v>1091</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -4437,7 +4437,7 @@
         <v>937</v>
       </c>
       <c r="B55" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -4445,7 +4445,7 @@
         <v>938</v>
       </c>
       <c r="B56" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -4453,7 +4453,7 @@
         <v>939</v>
       </c>
       <c r="B57" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -4461,7 +4461,7 @@
         <v>940</v>
       </c>
       <c r="B58" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -4469,7 +4469,7 @@
         <v>941</v>
       </c>
       <c r="B59" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -4477,7 +4477,7 @@
         <v>942</v>
       </c>
       <c r="B60" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -4485,7 +4485,7 @@
         <v>943</v>
       </c>
       <c r="B61" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -4493,7 +4493,7 @@
         <v>944</v>
       </c>
       <c r="B62" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -4501,7 +4501,7 @@
         <v>945</v>
       </c>
       <c r="B63" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -4509,7 +4509,7 @@
         <v>946</v>
       </c>
       <c r="B64" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -4517,7 +4517,7 @@
         <v>947</v>
       </c>
       <c r="B65" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -4525,7 +4525,7 @@
         <v>948</v>
       </c>
       <c r="B66" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -4533,7 +4533,7 @@
         <v>949</v>
       </c>
       <c r="B67" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -4541,7 +4541,7 @@
         <v>950</v>
       </c>
       <c r="B68" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -4549,7 +4549,7 @@
         <v>951</v>
       </c>
       <c r="B69" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -4557,7 +4557,7 @@
         <v>952</v>
       </c>
       <c r="B70" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -4565,7 +4565,7 @@
         <v>953</v>
       </c>
       <c r="B71" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -4573,7 +4573,7 @@
         <v>954</v>
       </c>
       <c r="B72" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -4581,7 +4581,7 @@
         <v>955</v>
       </c>
       <c r="B73" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -4589,7 +4589,7 @@
         <v>956</v>
       </c>
       <c r="B74" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -4597,7 +4597,7 @@
         <v>957</v>
       </c>
       <c r="B75" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -4605,7 +4605,7 @@
         <v>958</v>
       </c>
       <c r="B76" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -4613,7 +4613,7 @@
         <v>959</v>
       </c>
       <c r="B77" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -4621,7 +4621,7 @@
         <v>960</v>
       </c>
       <c r="B78" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -4629,7 +4629,7 @@
         <v>961</v>
       </c>
       <c r="B79" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -4637,7 +4637,7 @@
         <v>962</v>
       </c>
       <c r="B80" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -4645,7 +4645,7 @@
         <v>988</v>
       </c>
       <c r="B81" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -4653,7 +4653,7 @@
         <v>989</v>
       </c>
       <c r="B82" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -4661,7 +4661,7 @@
         <v>990</v>
       </c>
       <c r="B83" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -4669,7 +4669,7 @@
         <v>991</v>
       </c>
       <c r="B84" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -4677,7 +4677,7 @@
         <v>992</v>
       </c>
       <c r="B85" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -4685,7 +4685,7 @@
         <v>993</v>
       </c>
       <c r="B86" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -4693,7 +4693,7 @@
         <v>994</v>
       </c>
       <c r="B87" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -4701,7 +4701,7 @@
         <v>995</v>
       </c>
       <c r="B88" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -4709,7 +4709,7 @@
         <v>996</v>
       </c>
       <c r="B89" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -4717,7 +4717,7 @@
         <v>997</v>
       </c>
       <c r="B90" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -4725,7 +4725,7 @@
         <v>998</v>
       </c>
       <c r="B91" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -4733,7 +4733,7 @@
         <v>999</v>
       </c>
       <c r="B92" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -4741,7 +4741,7 @@
         <v>1000</v>
       </c>
       <c r="B93" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -4749,7 +4749,7 @@
         <v>1001</v>
       </c>
       <c r="B94" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -4757,7 +4757,7 @@
         <v>1002</v>
       </c>
       <c r="B95" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -4765,7 +4765,7 @@
         <v>1003</v>
       </c>
       <c r="B96" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -4773,7 +4773,7 @@
         <v>1004</v>
       </c>
       <c r="B97" t="s">
-        <v>1134</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -4781,7 +4781,7 @@
         <v>1005</v>
       </c>
       <c r="B98" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -4789,7 +4789,7 @@
         <v>1006</v>
       </c>
       <c r="B99" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -4797,7 +4797,7 @@
         <v>140</v>
       </c>
       <c r="B100" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -4805,7 +4805,7 @@
         <v>927</v>
       </c>
       <c r="B101" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -4813,7 +4813,7 @@
         <v>928</v>
       </c>
       <c r="B102" t="s">
-        <v>1139</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -4821,7 +4821,7 @@
         <v>929</v>
       </c>
       <c r="B103" t="s">
-        <v>1140</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -4829,7 +4829,7 @@
         <v>930</v>
       </c>
       <c r="B104" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -4837,7 +4837,7 @@
         <v>931</v>
       </c>
       <c r="B105" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -4845,7 +4845,7 @@
         <v>1023</v>
       </c>
       <c r="B106" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -4853,7 +4853,7 @@
         <v>1024</v>
       </c>
       <c r="B107" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -4861,7 +4861,7 @@
         <v>1025</v>
       </c>
       <c r="B108" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -4869,7 +4869,7 @@
         <v>1026</v>
       </c>
       <c r="B109" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -4877,7 +4877,7 @@
         <v>1027</v>
       </c>
       <c r="B110" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -4885,7 +4885,7 @@
         <v>1028</v>
       </c>
       <c r="B111" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -4893,7 +4893,7 @@
         <v>1029</v>
       </c>
       <c r="B112" t="s">
-        <v>1148</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -4901,7 +4901,7 @@
         <v>1030</v>
       </c>
       <c r="B113" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -4909,7 +4909,7 @@
         <v>1031</v>
       </c>
       <c r="B114" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -4917,7 +4917,7 @@
         <v>1032</v>
       </c>
       <c r="B115" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -4925,7 +4925,7 @@
         <v>1033</v>
       </c>
       <c r="B116" t="s">
-        <v>1152</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -4933,7 +4933,7 @@
         <v>1034</v>
       </c>
       <c r="B117" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -4941,7 +4941,7 @@
         <v>1035</v>
       </c>
       <c r="B118" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -4949,7 +4949,7 @@
         <v>1036</v>
       </c>
       <c r="B119" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -4957,7 +4957,7 @@
         <v>1037</v>
       </c>
       <c r="B120" t="s">
-        <v>1156</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -4965,7 +4965,7 @@
         <v>1038</v>
       </c>
       <c r="B121" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -4973,7 +4973,7 @@
         <v>1039</v>
       </c>
       <c r="B122" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -4981,7 +4981,7 @@
         <v>1040</v>
       </c>
       <c r="B123" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -4989,7 +4989,7 @@
         <v>1041</v>
       </c>
       <c r="B124" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -4997,7 +4997,7 @@
         <v>1042</v>
       </c>
       <c r="B125" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -5005,7 +5005,7 @@
         <v>1043</v>
       </c>
       <c r="B126" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -5013,7 +5013,7 @@
         <v>1044</v>
       </c>
       <c r="B127" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -5021,7 +5021,7 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
     </row>
   </sheetData>
@@ -8980,8 +8980,8 @@
         <v>0.30984615384615383</v>
       </c>
       <c r="E3" s="5">
-        <f>D3*60 +E11</f>
-        <v>37.902510121457489</v>
+        <f>D3*60</f>
+        <v>18.590769230769229</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -8997,7 +8997,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <f t="shared" si="0"/>
+        <f>($H$2*B4)/($I$2*C4)</f>
         <v>0.48923076923076925</v>
       </c>
       <c r="E4" s="5">
@@ -9028,8 +9028,8 @@
         <v>0.81538461538461537</v>
       </c>
       <c r="E5" s="5">
-        <f>D5*60 +E11</f>
-        <v>68.234817813765176</v>
+        <f>D5*60</f>
+        <v>48.92307692307692</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -9087,8 +9087,8 @@
         <v>0.38051282051282048</v>
       </c>
       <c r="E7" s="5">
-        <f>D7*60+E11</f>
-        <v>42.142510121457491</v>
+        <f>D7*60</f>
+        <v>22.830769230769228</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -9114,8 +9114,8 @@
         <v>0.44846153846153852</v>
       </c>
       <c r="E8" s="5">
-        <f>D8*60 + E11</f>
-        <v>46.219433198380571</v>
+        <f>D8*60</f>
+        <v>26.907692307692312</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
@@ -9424,8 +9424,7 @@
         <v>7.3384615384615381E-2</v>
       </c>
       <c r="E20" s="5">
-        <f t="shared" ref="E20" si="9">D20*60</f>
-        <v>4.4030769230769229</v>
+        <v>0.95499999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/FlowTracker.xlsx
+++ b/FlowTracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\PHSAhome2.phsabc.ehcnet.ca\Cassidy.Northway\Remote Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F222552E-8A28-4ECE-AD8C-BF9319FA0DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88780F9-E565-48E8-A616-D3D1849825F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4770" windowWidth="18240" windowHeight="28440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterSheet" sheetId="9" r:id="rId1"/>
@@ -3186,9 +3186,6 @@
     <t>28;29;30;0;0;B</t>
   </si>
   <si>
-    <t>0;126;126;0;0.955;0</t>
-  </si>
-  <si>
     <t>6;63;63;0;5.15;0</t>
   </si>
   <si>
@@ -3540,9 +3537,6 @@
     <t>27;101;102;0;6.12;AC</t>
   </si>
   <si>
-    <t>1;28;28;0;0.955;0</t>
-  </si>
-  <si>
     <t>48;10;10;0;0;0</t>
   </si>
   <si>
@@ -3562,6 +3556,12 @@
   </si>
   <si>
     <t>8;11;11;0;26.91;0</t>
+  </si>
+  <si>
+    <t>1;28;28;0;2.2;0</t>
+  </si>
+  <si>
+    <t>0;126;126;0;2.2;0</t>
   </si>
 </sst>
 </file>
@@ -4013,7 +4013,7 @@
         <v>936</v>
       </c>
       <c r="B2" t="s">
-        <v>1047</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4021,7 +4021,7 @@
         <v>935</v>
       </c>
       <c r="B3" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4029,7 +4029,7 @@
         <v>817</v>
       </c>
       <c r="B4" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4037,7 +4037,7 @@
         <v>844</v>
       </c>
       <c r="B5" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
         <v>845</v>
       </c>
       <c r="B6" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4053,7 +4053,7 @@
         <v>818</v>
       </c>
       <c r="B7" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4061,7 +4061,7 @@
         <v>807</v>
       </c>
       <c r="B8" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4069,7 +4069,7 @@
         <v>819</v>
       </c>
       <c r="B9" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -4077,7 +4077,7 @@
         <v>846</v>
       </c>
       <c r="B10" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -4085,7 +4085,7 @@
         <v>811</v>
       </c>
       <c r="B11" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4093,7 +4093,7 @@
         <v>848</v>
       </c>
       <c r="B12" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -4101,7 +4101,7 @@
         <v>847</v>
       </c>
       <c r="B13" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -4109,7 +4109,7 @@
         <v>1007</v>
       </c>
       <c r="B14" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -4117,7 +4117,7 @@
         <v>1008</v>
       </c>
       <c r="B15" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -4125,7 +4125,7 @@
         <v>1009</v>
       </c>
       <c r="B16" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -4133,7 +4133,7 @@
         <v>1010</v>
       </c>
       <c r="B17" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -4141,7 +4141,7 @@
         <v>1022</v>
       </c>
       <c r="B18" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -4149,7 +4149,7 @@
         <v>1011</v>
       </c>
       <c r="B19" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -4157,7 +4157,7 @@
         <v>1014</v>
       </c>
       <c r="B20" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -4165,7 +4165,7 @@
         <v>1015</v>
       </c>
       <c r="B21" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -4173,7 +4173,7 @@
         <v>1016</v>
       </c>
       <c r="B22" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -4181,7 +4181,7 @@
         <v>1017</v>
       </c>
       <c r="B23" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -4189,7 +4189,7 @@
         <v>1018</v>
       </c>
       <c r="B24" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -4197,7 +4197,7 @@
         <v>1019</v>
       </c>
       <c r="B25" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -4205,7 +4205,7 @@
         <v>1020</v>
       </c>
       <c r="B26" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -4213,7 +4213,7 @@
         <v>1021</v>
       </c>
       <c r="B27" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -4221,7 +4221,7 @@
         <v>1012</v>
       </c>
       <c r="B28" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -4229,7 +4229,7 @@
         <v>1013</v>
       </c>
       <c r="B29" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -4245,7 +4245,7 @@
         <v>964</v>
       </c>
       <c r="B31" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -4253,7 +4253,7 @@
         <v>965</v>
       </c>
       <c r="B32" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -4261,7 +4261,7 @@
         <v>966</v>
       </c>
       <c r="B33" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -4269,7 +4269,7 @@
         <v>967</v>
       </c>
       <c r="B34" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -4277,7 +4277,7 @@
         <v>968</v>
       </c>
       <c r="B35" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -4285,7 +4285,7 @@
         <v>969</v>
       </c>
       <c r="B36" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -4293,7 +4293,7 @@
         <v>970</v>
       </c>
       <c r="B37" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -4301,7 +4301,7 @@
         <v>971</v>
       </c>
       <c r="B38" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -4309,7 +4309,7 @@
         <v>972</v>
       </c>
       <c r="B39" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -4317,7 +4317,7 @@
         <v>973</v>
       </c>
       <c r="B40" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -4325,7 +4325,7 @@
         <v>974</v>
       </c>
       <c r="B41" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -4333,7 +4333,7 @@
         <v>975</v>
       </c>
       <c r="B42" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -4341,7 +4341,7 @@
         <v>976</v>
       </c>
       <c r="B43" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -4349,7 +4349,7 @@
         <v>977</v>
       </c>
       <c r="B44" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -4357,7 +4357,7 @@
         <v>978</v>
       </c>
       <c r="B45" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -4365,7 +4365,7 @@
         <v>979</v>
       </c>
       <c r="B46" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -4373,7 +4373,7 @@
         <v>980</v>
       </c>
       <c r="B47" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -4381,7 +4381,7 @@
         <v>981</v>
       </c>
       <c r="B48" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -4389,7 +4389,7 @@
         <v>982</v>
       </c>
       <c r="B49" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -4397,7 +4397,7 @@
         <v>983</v>
       </c>
       <c r="B50" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -4405,7 +4405,7 @@
         <v>984</v>
       </c>
       <c r="B51" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -4413,7 +4413,7 @@
         <v>985</v>
       </c>
       <c r="B52" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -4421,7 +4421,7 @@
         <v>986</v>
       </c>
       <c r="B53" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -4429,7 +4429,7 @@
         <v>987</v>
       </c>
       <c r="B54" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -4437,7 +4437,7 @@
         <v>937</v>
       </c>
       <c r="B55" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -4445,7 +4445,7 @@
         <v>938</v>
       </c>
       <c r="B56" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -4453,7 +4453,7 @@
         <v>939</v>
       </c>
       <c r="B57" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -4461,7 +4461,7 @@
         <v>940</v>
       </c>
       <c r="B58" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -4469,7 +4469,7 @@
         <v>941</v>
       </c>
       <c r="B59" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -4477,7 +4477,7 @@
         <v>942</v>
       </c>
       <c r="B60" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -4485,7 +4485,7 @@
         <v>943</v>
       </c>
       <c r="B61" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -4493,7 +4493,7 @@
         <v>944</v>
       </c>
       <c r="B62" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -4501,7 +4501,7 @@
         <v>945</v>
       </c>
       <c r="B63" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -4509,7 +4509,7 @@
         <v>946</v>
       </c>
       <c r="B64" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -4517,7 +4517,7 @@
         <v>947</v>
       </c>
       <c r="B65" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -4525,7 +4525,7 @@
         <v>948</v>
       </c>
       <c r="B66" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -4533,7 +4533,7 @@
         <v>949</v>
       </c>
       <c r="B67" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -4541,7 +4541,7 @@
         <v>950</v>
       </c>
       <c r="B68" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -4549,7 +4549,7 @@
         <v>951</v>
       </c>
       <c r="B69" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -4557,7 +4557,7 @@
         <v>952</v>
       </c>
       <c r="B70" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -4565,7 +4565,7 @@
         <v>953</v>
       </c>
       <c r="B71" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -4573,7 +4573,7 @@
         <v>954</v>
       </c>
       <c r="B72" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -4581,7 +4581,7 @@
         <v>955</v>
       </c>
       <c r="B73" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -4589,7 +4589,7 @@
         <v>956</v>
       </c>
       <c r="B74" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -4597,7 +4597,7 @@
         <v>957</v>
       </c>
       <c r="B75" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -4605,7 +4605,7 @@
         <v>958</v>
       </c>
       <c r="B76" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -4613,7 +4613,7 @@
         <v>959</v>
       </c>
       <c r="B77" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -4621,7 +4621,7 @@
         <v>960</v>
       </c>
       <c r="B78" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -4629,7 +4629,7 @@
         <v>961</v>
       </c>
       <c r="B79" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -4637,7 +4637,7 @@
         <v>962</v>
       </c>
       <c r="B80" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -4645,7 +4645,7 @@
         <v>988</v>
       </c>
       <c r="B81" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -4653,7 +4653,7 @@
         <v>989</v>
       </c>
       <c r="B82" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -4661,7 +4661,7 @@
         <v>990</v>
       </c>
       <c r="B83" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -4669,7 +4669,7 @@
         <v>991</v>
       </c>
       <c r="B84" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -4677,7 +4677,7 @@
         <v>992</v>
       </c>
       <c r="B85" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -4685,7 +4685,7 @@
         <v>993</v>
       </c>
       <c r="B86" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -4693,7 +4693,7 @@
         <v>994</v>
       </c>
       <c r="B87" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -4701,7 +4701,7 @@
         <v>995</v>
       </c>
       <c r="B88" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -4709,7 +4709,7 @@
         <v>996</v>
       </c>
       <c r="B89" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -4717,7 +4717,7 @@
         <v>997</v>
       </c>
       <c r="B90" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -4725,7 +4725,7 @@
         <v>998</v>
       </c>
       <c r="B91" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -4733,7 +4733,7 @@
         <v>999</v>
       </c>
       <c r="B92" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -4741,7 +4741,7 @@
         <v>1000</v>
       </c>
       <c r="B93" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -4749,7 +4749,7 @@
         <v>1001</v>
       </c>
       <c r="B94" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -4757,7 +4757,7 @@
         <v>1002</v>
       </c>
       <c r="B95" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -4765,7 +4765,7 @@
         <v>1003</v>
       </c>
       <c r="B96" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -4773,7 +4773,7 @@
         <v>1004</v>
       </c>
       <c r="B97" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -4781,7 +4781,7 @@
         <v>1005</v>
       </c>
       <c r="B98" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -4789,7 +4789,7 @@
         <v>1006</v>
       </c>
       <c r="B99" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -4797,7 +4797,7 @@
         <v>140</v>
       </c>
       <c r="B100" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -4805,7 +4805,7 @@
         <v>927</v>
       </c>
       <c r="B101" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -4813,7 +4813,7 @@
         <v>928</v>
       </c>
       <c r="B102" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -4821,7 +4821,7 @@
         <v>929</v>
       </c>
       <c r="B103" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -4829,7 +4829,7 @@
         <v>930</v>
       </c>
       <c r="B104" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -4837,7 +4837,7 @@
         <v>931</v>
       </c>
       <c r="B105" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -4845,7 +4845,7 @@
         <v>1023</v>
       </c>
       <c r="B106" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -4853,7 +4853,7 @@
         <v>1024</v>
       </c>
       <c r="B107" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -4861,7 +4861,7 @@
         <v>1025</v>
       </c>
       <c r="B108" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -4869,7 +4869,7 @@
         <v>1026</v>
       </c>
       <c r="B109" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -4877,7 +4877,7 @@
         <v>1027</v>
       </c>
       <c r="B110" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -4885,7 +4885,7 @@
         <v>1028</v>
       </c>
       <c r="B111" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -4893,7 +4893,7 @@
         <v>1029</v>
       </c>
       <c r="B112" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -4901,7 +4901,7 @@
         <v>1030</v>
       </c>
       <c r="B113" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -4909,7 +4909,7 @@
         <v>1031</v>
       </c>
       <c r="B114" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -4917,7 +4917,7 @@
         <v>1032</v>
       </c>
       <c r="B115" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -4925,7 +4925,7 @@
         <v>1033</v>
       </c>
       <c r="B116" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -4933,7 +4933,7 @@
         <v>1034</v>
       </c>
       <c r="B117" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -4941,7 +4941,7 @@
         <v>1035</v>
       </c>
       <c r="B118" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -4949,7 +4949,7 @@
         <v>1036</v>
       </c>
       <c r="B119" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -4957,7 +4957,7 @@
         <v>1037</v>
       </c>
       <c r="B120" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -4965,7 +4965,7 @@
         <v>1038</v>
       </c>
       <c r="B121" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -4973,7 +4973,7 @@
         <v>1039</v>
       </c>
       <c r="B122" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -4981,7 +4981,7 @@
         <v>1040</v>
       </c>
       <c r="B123" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -4989,7 +4989,7 @@
         <v>1041</v>
       </c>
       <c r="B124" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -4997,7 +4997,7 @@
         <v>1042</v>
       </c>
       <c r="B125" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -5005,7 +5005,7 @@
         <v>1043</v>
       </c>
       <c r="B126" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -5013,7 +5013,7 @@
         <v>1044</v>
       </c>
       <c r="B127" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -5021,7 +5021,7 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
   </sheetData>
@@ -9024,7 +9024,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <f t="shared" si="0"/>
+        <f>($H$2*B5)/($I$2*C5)</f>
         <v>0.81538461538461537</v>
       </c>
       <c r="E5" s="5">

--- a/FlowTracker.xlsx
+++ b/FlowTracker.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\PHSAhome2.phsabc.ehcnet.ca\Cassidy.Northway\Remote Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88780F9-E565-48E8-A616-D3D1849825F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824E204E-ACC2-438D-ACC6-7EB018D5B9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterSheet" sheetId="9" r:id="rId1"/>
     <sheet name="arteries" sheetId="1" r:id="rId2"/>
-    <sheet name="veins-sup" sheetId="2" r:id="rId3"/>
-    <sheet name="veins-inf" sheetId="5" r:id="rId4"/>
-    <sheet name="A-V Mapping" sheetId="6" r:id="rId5"/>
-    <sheet name="Dwell Time Calcs" sheetId="7" r:id="rId6"/>
-    <sheet name="Pulm" sheetId="8" r:id="rId7"/>
-    <sheet name="PulmArtOld" sheetId="4" r:id="rId8"/>
+    <sheet name="arteries_old" sheetId="10" r:id="rId3"/>
+    <sheet name="veins-sup" sheetId="2" r:id="rId4"/>
+    <sheet name="veins-inf" sheetId="5" r:id="rId5"/>
+    <sheet name="A-V Mapping" sheetId="6" r:id="rId6"/>
+    <sheet name="Dwell Time Calcs" sheetId="7" r:id="rId7"/>
+    <sheet name="Pulm" sheetId="8" r:id="rId8"/>
+    <sheet name="PulmArtOld" sheetId="4" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2768" uniqueCount="1173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2898" uniqueCount="1177">
   <si>
     <t>Filename</t>
   </si>
@@ -3562,6 +3563,18 @@
   </si>
   <si>
     <t>0;126;126;0;2.2;0</t>
+  </si>
+  <si>
+    <t>left_vertebral_arteries, left_arm_artery</t>
+  </si>
+  <si>
+    <t>right_subclavian_artery, left_external_iliac_artery,splenic_artery, superior_mesenteric_artery, left_common_cartoid_artery, left_subclavian_artery, inferior_mesenteric_artery, right_external_iliac_artery,  left_superior_renal_artery,  right_superior_renal_artery</t>
+  </si>
+  <si>
+    <t>arteries10,right_arm_artery, right_carotid_artery</t>
+  </si>
+  <si>
+    <t>left_gastric_artery, common_hepatic_artery</t>
   </si>
 </sst>
 </file>
@@ -3654,7 +3667,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5031,6 +5058,484 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" customWidth="1"/>
+    <col min="4" max="4" width="126.85546875" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" customWidth="1"/>
+    <col min="7" max="7" width="25.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E2" t="s">
+        <v>688</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E9" t="s">
+        <v>657</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>687</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
+        <v>763</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" t="s">
+        <v>127</v>
+      </c>
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" t="s">
+        <v>127</v>
+      </c>
+      <c r="G17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>367</v>
+      </c>
+      <c r="B19" t="s">
+        <v>388</v>
+      </c>
+      <c r="C19" t="s">
+        <v>3</v>
+      </c>
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>625</v>
+      </c>
+      <c r="B20" t="s">
+        <v>637</v>
+      </c>
+      <c r="C20" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>646</v>
+      </c>
+      <c r="B21" t="s">
+        <v>646</v>
+      </c>
+      <c r="C21" t="s">
+        <v>657</v>
+      </c>
+      <c r="D21" t="s">
+        <v>656</v>
+      </c>
+      <c r="G21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>653</v>
+      </c>
+      <c r="B22" t="s">
+        <v>657</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" t="s">
+        <v>646</v>
+      </c>
+      <c r="G22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>656</v>
+      </c>
+      <c r="B23" t="s">
+        <v>656</v>
+      </c>
+      <c r="C23" t="s">
+        <v>646</v>
+      </c>
+      <c r="G23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>661</v>
+      </c>
+      <c r="B24" t="s">
+        <v>661</v>
+      </c>
+      <c r="C24" t="s">
+        <v>687</v>
+      </c>
+      <c r="G24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>675</v>
+      </c>
+      <c r="B25" t="s">
+        <v>687</v>
+      </c>
+      <c r="C25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" t="s">
+        <v>679</v>
+      </c>
+      <c r="G25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>679</v>
+      </c>
+      <c r="B26" t="s">
+        <v>679</v>
+      </c>
+      <c r="C26" t="s">
+        <v>687</v>
+      </c>
+      <c r="G26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="G2:G26">
+    <cfRule type="containsBlanks" dxfId="5" priority="1">
+      <formula>LEN(TRIM(G2))=0</formula>
+    </cfRule>
+    <cfRule type="notContainsBlanks" dxfId="4" priority="2">
+      <formula>LEN(TRIM(G2))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{737C032F-21A6-48EB-86EF-B435E59BCF04}">
   <dimension ref="A1:G179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7758,7 +8263,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G2:G179">
     <cfRule type="containsBlanks" dxfId="3" priority="1">
       <formula>LEN(TRIM(G2))=0</formula>
@@ -7772,7 +8276,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7976,7 +8480,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E258076-C214-41D6-BCD6-F667F1858984}">
   <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8139,7 +8643,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{188388E5-F9D8-4148-BF34-9C51095EB628}">
   <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8887,7 +9391,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F665A280-B941-4509-8B0A-1E2E1E43C816}">
   <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9433,7 +9937,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A49E26-2F33-4C48-B568-5BD877D54B87}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9497,7 +10001,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83BDF3EF-B0DD-4EA1-9C5E-4B5CEDCAFD48}">
   <dimension ref="A1:G400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/FlowTracker.xlsx
+++ b/FlowTracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\PHSAhome2.phsabc.ehcnet.ca\Cassidy.Northway\Remote Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824E204E-ACC2-438D-ACC6-7EB018D5B9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E329C6BD-785D-4677-A0F1-CE3FF737FB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4770" windowWidth="18240" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterSheet" sheetId="9" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2898" uniqueCount="1177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2898" uniqueCount="1179">
   <si>
     <t>Filename</t>
   </si>
@@ -3575,6 +3575,12 @@
   </si>
   <si>
     <t>left_gastric_artery, common_hepatic_artery</t>
+  </si>
+  <si>
+    <t>arteries_lleg6, arteries_lleg17</t>
+  </si>
+  <si>
+    <t>arteries_rleg1, arteries_rleg23</t>
   </si>
 </sst>
 </file>
@@ -5359,7 +5365,7 @@
         <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>1177</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -5466,7 +5472,7 @@
         <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>679</v>
+        <v>1178</v>
       </c>
       <c r="G25" t="s">
         <v>11</v>

--- a/FlowTracker.xlsx
+++ b/FlowTracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\PHSAhome2.phsabc.ehcnet.ca\Cassidy.Northway\Remote Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E329C6BD-785D-4677-A0F1-CE3FF737FB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5ACCEB-E6BC-4D03-BF04-F989F0091540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4770" windowWidth="18240" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4770" windowWidth="18240" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterSheet" sheetId="9" r:id="rId1"/>
